--- a/test/excel/xlsx/saved/arrays-6.xlsx
+++ b/test/excel/xlsx/saved/arrays-6.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11004"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E434351-2631-AB46-8E56-5BB9DD2C8660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A97907D-368E-9244-A24B-8F0E5EDBA368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -216,6 +216,18 @@
     <t>1,5</t>
   </si>
   <si>
+    <t>lift:PRICE#7</t>
+  </si>
+  <si>
+    <t>lift:PRICE#8</t>
+  </si>
+  <si>
+    <t>lift:PRICE#9</t>
+  </si>
+  <si>
+    <t>lift:PRICE#10</t>
+  </si>
+  <si>
     <t>lift:PRICE#11</t>
   </si>
   <si>
@@ -1402,18 +1414,6 @@
   </si>
   <si>
     <t>lift:YIELD#12</t>
-  </si>
-  <si>
-    <t>lift:YIELD#13</t>
-  </si>
-  <si>
-    <t>lift:YIELD#14</t>
-  </si>
-  <si>
-    <t>lift:YIELDDISC#1</t>
-  </si>
-  <si>
-    <t>lift:YIELDDISC#2</t>
   </si>
   <si>
     <t>end</t>
@@ -3047,7 +3047,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="e" cm="1">
-        <f t="array" ref="A1">PRICE(DATE(2008,2,15),DATE(2017,11,15),0.0575,0.065,100,D!B1:B2,0)</f>
+        <f t="array" ref="A1">PRICE(DATE(2008,2,15),DATE(2017,11,15),0.0575,D!B1:B2,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B1">
@@ -3068,7 +3068,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A2" ca="1">PRICE(DATE(2008,2,15),DATE(2017,11,15),0.0575,0.065,100,{1;2},0)</f>
+        <f t="array" aca="1" ref="A2" ca="1">PRICE(DATE(2008,2,15),DATE(2017,11,15),0.0575,{1;2},100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B2">
@@ -3089,7 +3089,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="e" cm="1">
-        <f t="array" ref="A3">PRICE(DATE(2008,2,15),DATE(2017,11,15),0.0575,0.065,100,2,D!B1:B2)</f>
+        <f t="array" ref="A3">PRICE(DATE(2008,2,15),DATE(2017,11,15),0.0575,0.065,D!B1:B2,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B3">
@@ -3110,7 +3110,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A4" ca="1">PRICE(DATE(2008,2,15),DATE(2017,11,15),0.0575,0.065,100,2,{1;2})</f>
+        <f t="array" aca="1" ref="A4" ca="1">PRICE(DATE(2008,2,15),DATE(2017,11,15),0.0575,0.065,{1;2},2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B4">
@@ -3131,7 +3131,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="e" cm="1">
-        <f t="array" ref="A5">PRICEDISC(D!B1:B2,39508,0.0525,100,2)</f>
+        <f t="array" ref="A5">PRICE(DATE(2008,2,15),DATE(2017,11,15),0.0575,0.065,100,D!B1:B2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B5">
@@ -3152,7 +3152,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A6" ca="1">PRICEDISC({1;2},39508,0.0525,100,2)</f>
+        <f t="array" aca="1" ref="A6" ca="1">PRICE(DATE(2008,2,15),DATE(2017,11,15),0.0575,0.065,100,{1;2},0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B6">
@@ -3173,7 +3173,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="e" cm="1">
-        <f t="array" ref="A7">PRICEDISC(39494,D!B1:B2,0.0525,100,2)</f>
+        <f t="array" ref="A7">PRICE(DATE(2008,2,15),DATE(2017,11,15),0.0575,0.065,100,2,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B7">
@@ -3194,7 +3194,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A8" ca="1">PRICEDISC(39494,{1;2},0.0525,100,2)</f>
+        <f t="array" aca="1" ref="A8" ca="1">PRICE(DATE(2008,2,15),DATE(2017,11,15),0.0575,0.065,100,2,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B8">
@@ -3215,7 +3215,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="e" cm="1">
-        <f t="array" ref="A9">PRICEDISC(39494,39508,D!B1:B2,100,2)</f>
+        <f t="array" ref="A9">PRICEDISC(D!B1:B2,39508,0.0525,100,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B9">
@@ -3236,7 +3236,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A10" ca="1">PRICEDISC(39494,39508,{1;2},100,2)</f>
+        <f t="array" aca="1" ref="A10" ca="1">PRICEDISC({1;2},39508,0.0525,100,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B10">
@@ -3257,7 +3257,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="e" cm="1">
-        <f t="array" ref="A11">PRICEDISC(39494,39508,0.0525,D!B1:B2,2)</f>
+        <f t="array" ref="A11">PRICEDISC(39494,D!B1:B2,0.0525,100,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B11">
@@ -3278,7 +3278,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A12" ca="1">PRICEDISC(39494,39508,0.0525,{1;2},2)</f>
+        <f t="array" aca="1" ref="A12" ca="1">PRICEDISC(39494,{1;2},0.0525,100,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B12">
@@ -3299,7 +3299,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="e" cm="1">
-        <f t="array" ref="A13">PRICEDISC(39494,39508,0.0525,100,D!B1:B2)</f>
+        <f t="array" ref="A13">PRICEDISC(39494,39508,D!B1:B2,100,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B13">
@@ -3320,7 +3320,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A14" ca="1">PRICEDISC(39494,39508,0.0525,100,{1;2})</f>
+        <f t="array" aca="1" ref="A14" ca="1">PRICEDISC(39494,39508,{1;2},100,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B14">
@@ -3341,7 +3341,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="e" cm="1">
-        <f t="array" ref="A15">PRICEMAT(D!B1:B2,DATE(2008,4,13),DATE(2007,11,11),0.061,0.061,0)</f>
+        <f t="array" ref="A15">PRICEDISC(39494,39508,0.0525,D!B1:B2,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B15">
@@ -3362,7 +3362,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A16" ca="1">PRICEMAT({1;2},DATE(2008,4,13),DATE(2007,11,11),0.061,0.061,0)</f>
+        <f t="array" aca="1" ref="A16" ca="1">PRICEDISC(39494,39508,0.0525,{1;2},2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B16">
@@ -3383,7 +3383,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="e" cm="1">
-        <f t="array" ref="A17">PRICEMAT(DATE(2008,2,15),D!B1:B2,DATE(2007,11,11),0.061,0.061,0)</f>
+        <f t="array" ref="A17">PRICEDISC(39494,39508,0.0525,100,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B17">
@@ -3404,7 +3404,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A18" ca="1">PRICEMAT(DATE(2008,2,15),{1;2},DATE(2007,11,11),0.061,0.061,0)</f>
+        <f t="array" aca="1" ref="A18" ca="1">PRICEDISC(39494,39508,0.0525,100,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B18">
@@ -3425,7 +3425,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="e" cm="1">
-        <f t="array" ref="A19">PRICEMAT(DATE(2008,2,15),DATE(2008,4,13),D!B1:B2,0.061,0.061,0)</f>
+        <f t="array" ref="A19">PRICEMAT(D!B1:B2,DATE(2008,4,13),DATE(2007,11,11),0.061,0.061,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B19">
@@ -3446,7 +3446,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A20" ca="1">PRICEMAT(DATE(2008,2,15),DATE(2008,4,13),{1;2},0.061,0.061,0)</f>
+        <f t="array" aca="1" ref="A20" ca="1">PRICEMAT({1;2},DATE(2008,4,13),DATE(2007,11,11),0.061,0.061,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B20">
@@ -3467,7 +3467,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="e" cm="1">
-        <f t="array" ref="A21">PRICEMAT(DATE(2008,2,15),DATE(2008,4,13),DATE(2007,11,11),D!B1:B2,0.061,0)</f>
+        <f t="array" ref="A21">PRICEMAT(DATE(2008,2,15),D!B1:B2,DATE(2007,11,11),0.061,0.061,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B21">
@@ -3488,7 +3488,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A22" ca="1">PRICEMAT(DATE(2008,2,15),DATE(2008,4,13),DATE(2007,11,11),{1;2},0.061,0)</f>
+        <f t="array" aca="1" ref="A22" ca="1">PRICEMAT(DATE(2008,2,15),{1;2},DATE(2007,11,11),0.061,0.061,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B22">
@@ -3509,7 +3509,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="e" cm="1">
-        <f t="array" ref="A23">PRICEMAT(DATE(2008,2,15),DATE(2008,4,13),DATE(2007,11,11),0.061,D!B1:B2,0)</f>
+        <f t="array" ref="A23">PRICEMAT(DATE(2008,2,15),DATE(2008,4,13),D!B1:B2,0.061,0.061,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B23">
@@ -3530,7 +3530,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A24" ca="1">PRICEMAT(DATE(2008,2,15),DATE(2008,4,13),DATE(2007,11,11),0.061,{1;2},0)</f>
+        <f t="array" aca="1" ref="A24" ca="1">PRICEMAT(DATE(2008,2,15),DATE(2008,4,13),{1;2},0.061,0.061,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B24">
@@ -3551,7 +3551,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="e" cm="1">
-        <f t="array" ref="A25">PRICEMAT(DATE(2008,2,15),DATE(2008,4,13),DATE(2007,11,11),0.061,0.061,D!B1:B2)</f>
+        <f t="array" ref="A25">PRICEMAT(DATE(2008,2,15),DATE(2008,4,13),DATE(2007,11,11),D!B1:B2,0.061,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B25">
@@ -3572,7 +3572,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A26" ca="1">PRICEMAT(DATE(2008,2,15),DATE(2008,4,13),DATE(2007,11,11),0.061,0.061,{1;2})</f>
+        <f t="array" aca="1" ref="A26" ca="1">PRICEMAT(DATE(2008,2,15),DATE(2008,4,13),DATE(2007,11,11),{1;2},0.061,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B26">
@@ -3592,20 +3592,20 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A27" ca="1">PROB(D!AH1:AH4,D!AI1:AI4,D!B1:B2)</f>
+      <c r="A27" t="e" cm="1">
+        <f t="array" ref="A27">PRICEMAT(DATE(2008,2,15),DATE(2008,4,13),DATE(2007,11,11),0.061,D!B1:B2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B27">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="C27">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D27" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="E27" t="s">
@@ -3614,7 +3614,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A28" ca="1">PROB(D!AH1:AH4,D!AI1:AI4,{1;2})</f>
+        <f t="array" aca="1" ref="A28" ca="1">PRICEMAT(DATE(2008,2,15),DATE(2008,4,13),DATE(2007,11,11),0.061,{1;2},0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B28">
@@ -3634,20 +3634,20 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A29" ca="1">PROPER(D!B1:B2)</f>
+      <c r="A29" t="e" cm="1">
+        <f t="array" ref="A29">PRICEMAT(DATE(2008,2,15),DATE(2008,4,13),DATE(2007,11,11),0.061,0.061,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B29">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="C29">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D29" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="E29" t="s">
@@ -3656,7 +3656,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A30" ca="1">PROPER({1;2})</f>
+        <f t="array" aca="1" ref="A30" ca="1">PRICEMAT(DATE(2008,2,15),DATE(2008,4,13),DATE(2007,11,11),0.061,0.061,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B30">
@@ -3677,7 +3677,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A31" ca="1">PV(D!B1:B2,240,500,0,0)</f>
+        <f t="array" aca="1" ref="A31" ca="1">PROB(D!AH1:AH4,D!AI1:AI4,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B31">
@@ -3698,7 +3698,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A32" ca="1">PV({1;2},240,500,0,0)</f>
+        <f t="array" aca="1" ref="A32" ca="1">PROB(D!AH1:AH4,D!AI1:AI4,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B32">
@@ -3719,7 +3719,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A33" ca="1">PV(0.00666666666666667,D!B1:B2,500,0,0)</f>
+        <f t="array" aca="1" ref="A33" ca="1">PROPER(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B33">
@@ -3740,7 +3740,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A34" ca="1">PV(0.00666666666666667,{1;2},500,0,0)</f>
+        <f t="array" aca="1" ref="A34" ca="1">PROPER({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B34">
@@ -3761,7 +3761,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A35" ca="1">PV(0.00666666666666667,240,D!B1:B2,0,0)</f>
+        <f t="array" aca="1" ref="A35" ca="1">PV(D!B1:B2,240,500,0,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B35">
@@ -3782,7 +3782,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A36" ca="1">PV(0.00666666666666667,240,{1;2},0,0)</f>
+        <f t="array" aca="1" ref="A36" ca="1">PV({1;2},240,500,0,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B36">
@@ -3803,7 +3803,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A37" ca="1">PV(0.00666666666666667,240,500,D!B1:B2,0)</f>
+        <f t="array" aca="1" ref="A37" ca="1">PV(0.00666666666666667,D!B1:B2,500,0,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B37">
@@ -3824,7 +3824,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A38" ca="1">PV(0.00666666666666667,240,500,{1;2},0)</f>
+        <f t="array" aca="1" ref="A38" ca="1">PV(0.00666666666666667,{1;2},500,0,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B38">
@@ -3845,7 +3845,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A39" ca="1">PV(0.00666666666666667,240,500,0,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A39" ca="1">PV(0.00666666666666667,240,D!B1:B2,0,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B39">
@@ -3866,7 +3866,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A40" ca="1">PV(0.00666666666666667,240,500,0,{1;2})</f>
+        <f t="array" aca="1" ref="A40" ca="1">PV(0.00666666666666667,240,{1;2},0,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B40">
@@ -3887,7 +3887,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A41" ca="1">QUARTILE(D!B1:B8,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A41" ca="1">PV(0.00666666666666667,240,500,D!B1:B2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B41">
@@ -3908,7 +3908,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A42" ca="1">QUARTILE(D!B1:B8,{1;2})</f>
+        <f t="array" aca="1" ref="A42" ca="1">PV(0.00666666666666667,240,500,{1;2},0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B42">
@@ -3929,7 +3929,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A43" ca="1">_xlfn.QUARTILE.EXC(D!B1:B8,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A43" ca="1">PV(0.00666666666666667,240,500,0,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B43">
@@ -3950,7 +3950,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A44" ca="1">_xlfn.QUARTILE.EXC(D!B1:B8,{1;2})</f>
+        <f t="array" aca="1" ref="A44" ca="1">PV(0.00666666666666667,240,500,0,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B44">
@@ -3971,7 +3971,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A45" ca="1">_xlfn.QUARTILE.INC(D!B1:B8,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A45" ca="1">QUARTILE(D!B1:B8,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B45">
@@ -3992,7 +3992,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A46" ca="1">_xlfn.QUARTILE.INC(D!B1:B8,{1;2})</f>
+        <f t="array" aca="1" ref="A46" ca="1">QUARTILE(D!B1:B8,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B46">
@@ -4012,146 +4012,146 @@
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" t="e" cm="1">
-        <f t="array" ref="A47">QUOTIENT(D!B1:B2,2)</f>
+      <c r="A47" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A47" ca="1">_xlfn.QUARTILE.EXC(D!B1:B8,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B47">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C47">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D47" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="E47" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A48" ca="1">_xlfn.QUARTILE.EXC(D!B1:B8,{1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B48">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C48">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D48" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="E48" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A49" ca="1">_xlfn.QUARTILE.INC(D!B1:B8,D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B49">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C49">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D49" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="E49" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A50" ca="1">_xlfn.QUARTILE.INC(D!B1:B8,{1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B50">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C50">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D50" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="E50" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" t="e" cm="1">
+        <f t="array" ref="A51">QUOTIENT(D!B1:B2,2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B51">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C47">
+      <c r="C51">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D47" t="str">
+      <c r="D51" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="E47" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A48" ca="1">QUOTIENT({1;2},2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B48">
+      <c r="E51" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A52" ca="1">QUOTIENT({1;2},2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B52">
         <f t="shared" ca="1" si="0"/>
         <v>9</v>
       </c>
-      <c r="C48">
+      <c r="C52">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="D48" t="str">
+      <c r="D52" t="str">
         <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
-      <c r="E48" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" t="e" cm="1">
-        <f t="array" ref="A49">QUOTIENT(5,D!B1:B2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B49">
+      <c r="E52" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" t="e" cm="1">
+        <f t="array" ref="A53">QUOTIENT(5,D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B53">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C49">
+      <c r="C53">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D49" t="str">
+      <c r="D53" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="E49" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A50" ca="1">QUOTIENT(5,{1;2})</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B50">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C50">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D50" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="E50" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A51" ca="1">RADIANS(D!B1:B2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B51">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C51">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D51" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="E51" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A52" ca="1">RADIANS({1;2})</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B52">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C52">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D52" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="E52" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A53" ca="1">RANK(D!B1:B2,D!B1:B8)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B53">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C53">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D53" t="str">
-        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="E53" t="s">
@@ -4160,7 +4160,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A54" ca="1">RANK({1;2},D!B1:B8)</f>
+        <f t="array" aca="1" ref="A54" ca="1">QUOTIENT(5,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B54">
@@ -4181,7 +4181,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A55" ca="1">_xlfn.RANK.AVG(D!B1:B2,D!BE1:BE7)</f>
+        <f t="array" aca="1" ref="A55" ca="1">RADIANS(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B55">
@@ -4202,7 +4202,7 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A56" ca="1">_xlfn.RANK.AVG({1;2},D!BE1:BE7)</f>
+        <f t="array" aca="1" ref="A56" ca="1">RADIANS({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B56">
@@ -4223,7 +4223,7 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A57" ca="1">_xlfn.RANK.EQ(D!B1:B2,D!BE1:BE7)</f>
+        <f t="array" aca="1" ref="A57" ca="1">RANK(D!B1:B2,D!B1:B8)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B57">
@@ -4244,7 +4244,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A58" ca="1">_xlfn.RANK.EQ({1;2},D!BE1:BE7)</f>
+        <f t="array" aca="1" ref="A58" ca="1">RANK({1;2},D!B1:B8)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B58">
@@ -4265,7 +4265,7 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A59" ca="1">RATE(D!B1:B2,-200,8000)</f>
+        <f t="array" aca="1" ref="A59" ca="1">_xlfn.RANK.AVG(D!B1:B2,D!BE1:BE7)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B59">
@@ -4286,7 +4286,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A60" ca="1">RATE({1;2},-200,8000)</f>
+        <f t="array" aca="1" ref="A60" ca="1">_xlfn.RANK.AVG({1;2},D!BE1:BE7)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B60">
@@ -4307,7 +4307,7 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A61" ca="1">RATE(48,D!B1:B2,8000)</f>
+        <f t="array" aca="1" ref="A61" ca="1">_xlfn.RANK.EQ(D!B1:B2,D!BE1:BE7)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B61">
@@ -4328,7 +4328,7 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A62" ca="1">RATE(48,{1;2},8000)</f>
+        <f t="array" aca="1" ref="A62" ca="1">_xlfn.RANK.EQ({1;2},D!BE1:BE7)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B62">
@@ -4349,7 +4349,7 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A63" ca="1">RATE(48,-200,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A63" ca="1">RATE(D!B1:B2,-200,8000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B63">
@@ -4370,7 +4370,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A64" ca="1">RATE(48,-200,{1;2})</f>
+        <f t="array" aca="1" ref="A64" ca="1">RATE({1;2},-200,8000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B64">
@@ -4390,20 +4390,20 @@
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A65" t="e" cm="1">
-        <f t="array" ref="A65">RECEIVED(D!B1:B2,DATE(2008,5,15),1000000,0.0575,2)</f>
+      <c r="A65" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A65" ca="1">RATE(48,D!B1:B2,8000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B65">
-        <f t="shared" ref="B65:B128" si="3">IF(ISERROR(A65),ERROR.TYPE(A65),IF(ISNUMBER(A65),0,IF(ISLOGICAL(A65),IF(A65,-1,-2),IF(ISTEXT(A65),-3,-4))))</f>
-        <v>3</v>
+        <f t="shared" ref="B65:B128" ca="1" si="3">IF(ISERROR(A65),ERROR.TYPE(A65),IF(ISNUMBER(A65),0,IF(ISLOGICAL(A65),IF(A65,-1,-2),IF(ISTEXT(A65),-3,-4))))</f>
+        <v>9</v>
       </c>
       <c r="C65">
-        <f t="shared" ref="C65:C128" si="4">IF(ISNUMBER(A65),A65,0)</f>
+        <f t="shared" ref="C65:C128" ca="1" si="4">IF(ISNUMBER(A65),A65,0)</f>
         <v>0</v>
       </c>
       <c r="D65" t="str">
-        <f t="shared" ref="D65:D128" si="5">IF(ISTEXT(A65),A65,"")</f>
+        <f t="shared" ref="D65:D128" ca="1" si="5">IF(ISTEXT(A65),A65,"")</f>
         <v/>
       </c>
       <c r="E65" t="s">
@@ -4412,7 +4412,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A66" ca="1">RECEIVED({1;2},DATE(2008,5,15),1000000,0.0575,2)</f>
+        <f t="array" aca="1" ref="A66" ca="1">RATE(48,{1;2},8000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B66">
@@ -4432,20 +4432,20 @@
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A67" t="e" cm="1">
-        <f t="array" ref="A67">RECEIVED(DATE(2008,2,15),D!B1:B2,1000000,0.0575,2)</f>
+      <c r="A67" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A67" ca="1">RATE(48,-200,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B67">
-        <f t="shared" si="3"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>9</v>
       </c>
       <c r="C67">
-        <f t="shared" si="4"/>
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="D67" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="E67" t="s">
@@ -4454,7 +4454,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A68" ca="1">RECEIVED(DATE(2008,2,15),{1;2},1000000,0.0575,2)</f>
+        <f t="array" aca="1" ref="A68" ca="1">RATE(48,-200,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B68">
@@ -4475,7 +4475,7 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" t="e" cm="1">
-        <f t="array" ref="A69">RECEIVED(DATE(2008,2,15),DATE(2008,5,15),D!B1:B2,0.0575,2)</f>
+        <f t="array" ref="A69">RECEIVED(D!B1:B2,DATE(2008,5,15),1000000,0.0575,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B69">
@@ -4496,7 +4496,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A70" ca="1">RECEIVED(DATE(2008,2,15),DATE(2008,5,15),{1;2},0.0575,2)</f>
+        <f t="array" aca="1" ref="A70" ca="1">RECEIVED({1;2},DATE(2008,5,15),1000000,0.0575,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B70">
@@ -4517,7 +4517,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" t="e" cm="1">
-        <f t="array" ref="A71">RECEIVED(DATE(2008,2,15),DATE(2008,5,15),1000000,D!B1:B2,2)</f>
+        <f t="array" ref="A71">RECEIVED(DATE(2008,2,15),D!B1:B2,1000000,0.0575,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B71">
@@ -4538,7 +4538,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A72" ca="1">RECEIVED(DATE(2008,2,15),DATE(2008,5,15),1000000,{1;2},2)</f>
+        <f t="array" aca="1" ref="A72" ca="1">RECEIVED(DATE(2008,2,15),{1;2},1000000,0.0575,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B72">
@@ -4559,7 +4559,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" t="e" cm="1">
-        <f t="array" ref="A73">RECEIVED(DATE(2008,2,15),DATE(2008,5,15),1000000,0.0575,D!B1:B2)</f>
+        <f t="array" ref="A73">RECEIVED(DATE(2008,2,15),DATE(2008,5,15),D!B1:B2,0.0575,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B73">
@@ -4580,7 +4580,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A74" ca="1">RECEIVED(DATE(2008,2,15),DATE(2008,5,15),1000000,0.0575,{1;2})</f>
+        <f t="array" aca="1" ref="A74" ca="1">RECEIVED(DATE(2008,2,15),DATE(2008,5,15),{1;2},0.0575,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B74">
@@ -4600,20 +4600,20 @@
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A75" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A75" ca="1">REPLACE(D!B1:B2,6,5,"*")</f>
+      <c r="A75" t="e" cm="1">
+        <f t="array" ref="A75">RECEIVED(DATE(2008,2,15),DATE(2008,5,15),1000000,D!B1:B2,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B75">
-        <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <f t="shared" si="3"/>
+        <v>3</v>
       </c>
       <c r="C75">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D75" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="E75" t="s">
@@ -4622,7 +4622,7 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A76" ca="1">REPLACE({1;2},6,5,"*")</f>
+        <f t="array" aca="1" ref="A76" ca="1">RECEIVED(DATE(2008,2,15),DATE(2008,5,15),1000000,{1;2},2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B76">
@@ -4642,20 +4642,20 @@
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A77" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A77" ca="1">REPLACE("abcdefghijk",D!B1:B2,5,"*")</f>
+      <c r="A77" t="e" cm="1">
+        <f t="array" ref="A77">RECEIVED(DATE(2008,2,15),DATE(2008,5,15),1000000,0.0575,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B77">
-        <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <f t="shared" si="3"/>
+        <v>3</v>
       </c>
       <c r="C77">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D77" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="E77" t="s">
@@ -4664,7 +4664,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A78" ca="1">REPLACE("abcdefghijk",{1;2},5,"*")</f>
+        <f t="array" aca="1" ref="A78" ca="1">RECEIVED(DATE(2008,2,15),DATE(2008,5,15),1000000,0.0575,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B78">
@@ -4685,7 +4685,7 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A79" ca="1">REPLACE("abcdefghijk",6,D!B1:B2,"*")</f>
+        <f t="array" aca="1" ref="A79" ca="1">REPLACE(D!B1:B2,6,5,"*")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B79">
@@ -4706,7 +4706,7 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A80" ca="1">REPLACE("abcdefghijk",6,{1;2},"*")</f>
+        <f t="array" aca="1" ref="A80" ca="1">REPLACE({1;2},6,5,"*")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B80">
@@ -4727,7 +4727,7 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A81" ca="1">REPLACE("abcdefghijk",6,5,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A81" ca="1">REPLACE("abcdefghijk",D!B1:B2,5,"*")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B81">
@@ -4748,7 +4748,7 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A82" ca="1">REPLACE("abcdefghijk",6,5,{1;2})</f>
+        <f t="array" aca="1" ref="A82" ca="1">REPLACE("abcdefghijk",{1;2},5,"*")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B82">
@@ -4769,7 +4769,7 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A83" ca="1">REPLACEB(D!B1:B2,2,3,"x")</f>
+        <f t="array" aca="1" ref="A83" ca="1">REPLACE("abcdefghijk",6,D!B1:B2,"*")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B83">
@@ -4790,7 +4790,7 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A84" ca="1">REPLACEB({1;2},2,3,"x")</f>
+        <f t="array" aca="1" ref="A84" ca="1">REPLACE("abcdefghijk",6,{1;2},"*")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B84">
@@ -4811,7 +4811,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A85" ca="1">REPLACEB("abcdef",D!B1:B2,3,"x")</f>
+        <f t="array" aca="1" ref="A85" ca="1">REPLACE("abcdefghijk",6,5,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B85">
@@ -4832,7 +4832,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A86" ca="1">REPLACEB("abcdef",{1;2},3,"x")</f>
+        <f t="array" aca="1" ref="A86" ca="1">REPLACE("abcdefghijk",6,5,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B86">
@@ -4853,7 +4853,7 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A87" ca="1">REPLACEB("abcdef",2,D!B1:B2,"x")</f>
+        <f t="array" aca="1" ref="A87" ca="1">REPLACEB(D!B1:B2,2,3,"x")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B87">
@@ -4874,7 +4874,7 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A88" ca="1">REPLACEB("abcdef",2,{1;2},"x")</f>
+        <f t="array" aca="1" ref="A88" ca="1">REPLACEB({1;2},2,3,"x")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B88">
@@ -4895,7 +4895,7 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A89" ca="1">REPLACEB("abcdef",2,3,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A89" ca="1">REPLACEB("abcdef",D!B1:B2,3,"x")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B89">
@@ -4916,7 +4916,7 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A90" ca="1">REPLACEB("abcdef",2,3,{1;2})</f>
+        <f t="array" aca="1" ref="A90" ca="1">REPLACEB("abcdef",{1;2},3,"x")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B90">
@@ -4937,7 +4937,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A91" ca="1">REPT(D!B1:B2,3)</f>
+        <f t="array" aca="1" ref="A91" ca="1">REPLACEB("abcdef",2,D!B1:B2,"x")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B91">
@@ -4958,7 +4958,7 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A92" ca="1">REPT({1;2},3)</f>
+        <f t="array" aca="1" ref="A92" ca="1">REPLACEB("abcdef",2,{1;2},"x")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B92">
@@ -4979,7 +4979,7 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A93" ca="1">REPT("*-",D!B1:B2)</f>
+        <f t="array" aca="1" ref="A93" ca="1">REPLACEB("abcdef",2,3,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B93">
@@ -5000,7 +5000,7 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A94" ca="1">REPT("*-",{1;2})</f>
+        <f t="array" aca="1" ref="A94" ca="1">REPLACEB("abcdef",2,3,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B94">
@@ -5021,7 +5021,7 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A95" ca="1">RIGHT(D!B1:B2,5)</f>
+        <f t="array" aca="1" ref="A95" ca="1">REPT(D!B1:B2,3)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B95">
@@ -5042,7 +5042,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A96" ca="1">RIGHT({1;2},5)</f>
+        <f t="array" aca="1" ref="A96" ca="1">REPT({1;2},3)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B96">
@@ -5063,7 +5063,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A97" ca="1">RIGHT("Sale Price",D!B1:B2)</f>
+        <f t="array" aca="1" ref="A97" ca="1">REPT("*-",D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B97">
@@ -5084,7 +5084,7 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A98" ca="1">RIGHT("Sale Price",{1;2})</f>
+        <f t="array" aca="1" ref="A98" ca="1">REPT("*-",{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B98">
@@ -5105,7 +5105,7 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A99" ca="1">RIGHTB(D!B1:B2,2)</f>
+        <f t="array" aca="1" ref="A99" ca="1">RIGHT(D!B1:B2,5)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B99">
@@ -5126,7 +5126,7 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A100" ca="1">RIGHTB({1;2},2)</f>
+        <f t="array" aca="1" ref="A100" ca="1">RIGHT({1;2},5)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B100">
@@ -5147,7 +5147,7 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A101" ca="1">RIGHTB("abc",D!B1:B2)</f>
+        <f t="array" aca="1" ref="A101" ca="1">RIGHT("Sale Price",D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B101">
@@ -5168,7 +5168,7 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A102" ca="1">RIGHTB("abc",{1;2})</f>
+        <f t="array" aca="1" ref="A102" ca="1">RIGHT("Sale Price",{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B102">
@@ -5189,7 +5189,7 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A103" ca="1">ROMAN(D!B1:B2,0)</f>
+        <f t="array" aca="1" ref="A103" ca="1">RIGHTB(D!B1:B2,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B103">
@@ -5210,7 +5210,7 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A104" ca="1">ROMAN({1;2},0)</f>
+        <f t="array" aca="1" ref="A104" ca="1">RIGHTB({1;2},2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B104">
@@ -5231,7 +5231,7 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A105" ca="1">ROMAN(499,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A105" ca="1">RIGHTB("abc",D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B105">
@@ -5252,7 +5252,7 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A106" ca="1">ROMAN(499,{1;2})</f>
+        <f t="array" aca="1" ref="A106" ca="1">RIGHTB("abc",{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B106">
@@ -5273,7 +5273,7 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A107" ca="1">ROUND(D!B1:B2,1)</f>
+        <f t="array" aca="1" ref="A107" ca="1">ROMAN(D!B1:B2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B107">
@@ -5294,7 +5294,7 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A108" ca="1">ROUND({1;2},1)</f>
+        <f t="array" aca="1" ref="A108" ca="1">ROMAN({1;2},0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B108">
@@ -5315,7 +5315,7 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A109" ca="1">ROUND(2.15,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A109" ca="1">ROMAN(499,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B109">
@@ -5336,7 +5336,7 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A110" ca="1">ROUND(2.15,{1;2})</f>
+        <f t="array" aca="1" ref="A110" ca="1">ROMAN(499,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B110">
@@ -5357,7 +5357,7 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A111" ca="1">ROUNDDOWN(D!B1:B2,0)</f>
+        <f t="array" aca="1" ref="A111" ca="1">ROUND(D!B1:B2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B111">
@@ -5378,7 +5378,7 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A112" ca="1">ROUNDDOWN({1;2},0)</f>
+        <f t="array" aca="1" ref="A112" ca="1">ROUND({1;2},1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B112">
@@ -5399,7 +5399,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A113" ca="1">ROUNDDOWN(3.2,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A113" ca="1">ROUND(2.15,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B113">
@@ -5420,7 +5420,7 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A114" ca="1">ROUNDDOWN(3.2,{1;2})</f>
+        <f t="array" aca="1" ref="A114" ca="1">ROUND(2.15,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B114">
@@ -5441,7 +5441,7 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A115" ca="1">ROUNDUP(D!B1:B2,0)</f>
+        <f t="array" aca="1" ref="A115" ca="1">ROUNDDOWN(D!B1:B2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B115">
@@ -5462,7 +5462,7 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A116" ca="1">ROUNDUP({1;2},0)</f>
+        <f t="array" aca="1" ref="A116" ca="1">ROUNDDOWN({1;2},0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B116">
@@ -5483,7 +5483,7 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A117" ca="1">ROUNDUP(3.2,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A117" ca="1">ROUNDDOWN(3.2,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B117">
@@ -5504,7 +5504,7 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A118" ca="1">ROUNDUP(3.2,{1;2})</f>
+        <f t="array" aca="1" ref="A118" ca="1">ROUNDDOWN(3.2,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B118">
@@ -5525,7 +5525,7 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A119" ca="1">_xlfn.RRI(D!B1:B2,10000,11000)</f>
+        <f t="array" aca="1" ref="A119" ca="1">ROUNDUP(D!B1:B2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B119">
@@ -5546,7 +5546,7 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A120" ca="1">_xlfn.RRI({1;2},10000,11000)</f>
+        <f t="array" aca="1" ref="A120" ca="1">ROUNDUP({1;2},0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B120">
@@ -5567,7 +5567,7 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A121" ca="1">_xlfn.RRI(96,D!B1:B2,11000)</f>
+        <f t="array" aca="1" ref="A121" ca="1">ROUNDUP(3.2,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B121">
@@ -5588,7 +5588,7 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A122" ca="1">_xlfn.RRI(96,{1;2},11000)</f>
+        <f t="array" aca="1" ref="A122" ca="1">ROUNDUP(3.2,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B122">
@@ -5609,7 +5609,7 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A123" ca="1">_xlfn.RRI(96,10000,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A123" ca="1">_xlfn.RRI(D!B1:B2,10000,11000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B123">
@@ -5630,7 +5630,7 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A124" ca="1">_xlfn.RRI(96,10000,{1;2})</f>
+        <f t="array" aca="1" ref="A124" ca="1">_xlfn.RRI({1;2},10000,11000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B124">
@@ -5651,7 +5651,7 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A125" ca="1">SEARCH(D!B1:B2,"Statements",6)</f>
+        <f t="array" aca="1" ref="A125" ca="1">_xlfn.RRI(96,D!B1:B2,11000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B125">
@@ -5672,7 +5672,7 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A126" ca="1">SEARCH({1;2},"Statements",6)</f>
+        <f t="array" aca="1" ref="A126" ca="1">_xlfn.RRI(96,{1;2},11000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B126">
@@ -5693,7 +5693,7 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A127" ca="1">SEARCH("e",D!B1:B2,6)</f>
+        <f t="array" aca="1" ref="A127" ca="1">_xlfn.RRI(96,10000,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B127">
@@ -5714,7 +5714,7 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A128" ca="1">SEARCH("e",{1;2},6)</f>
+        <f t="array" aca="1" ref="A128" ca="1">_xlfn.RRI(96,10000,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B128">
@@ -5735,7 +5735,7 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A129" ca="1">SEARCH("e","Statements",D!B1:B2)</f>
+        <f t="array" aca="1" ref="A129" ca="1">SEARCH(D!B1:B2,"Statements",6)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B129">
@@ -5756,7 +5756,7 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A130" ca="1">SEARCH("e","Statements",{1;2})</f>
+        <f t="array" aca="1" ref="A130" ca="1">SEARCH({1;2},"Statements",6)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B130">
@@ -5777,7 +5777,7 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A131" ca="1">SEARCHB(D!B1:B2,"abc")</f>
+        <f t="array" aca="1" ref="A131" ca="1">SEARCH("e",D!B1:B2,6)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B131">
@@ -5798,7 +5798,7 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A132" ca="1">SEARCHB({1;2},"abc")</f>
+        <f t="array" aca="1" ref="A132" ca="1">SEARCH("e",{1;2},6)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B132">
@@ -5819,7 +5819,7 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A133" ca="1">SEARCHB("B",D!B1:B2)</f>
+        <f t="array" aca="1" ref="A133" ca="1">SEARCH("e","Statements",D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B133">
@@ -5840,7 +5840,7 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A134" ca="1">SEARCHB("B",{1;2})</f>
+        <f t="array" aca="1" ref="A134" ca="1">SEARCH("e","Statements",{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B134">
@@ -5861,7 +5861,7 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A135" ca="1">_xlfn.SEC(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A135" ca="1">SEARCHB(D!B1:B2,"abc")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B135">
@@ -5882,7 +5882,7 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A136" ca="1">_xlfn.SEC({1;2})</f>
+        <f t="array" aca="1" ref="A136" ca="1">SEARCHB({1;2},"abc")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B136">
@@ -5903,7 +5903,7 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A137" ca="1">_xlfn.SECH(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A137" ca="1">SEARCHB("B",D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B137">
@@ -5924,7 +5924,7 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A138" ca="1">_xlfn.SECH({1;2})</f>
+        <f t="array" aca="1" ref="A138" ca="1">SEARCHB("B",{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B138">
@@ -5945,7 +5945,7 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A139" ca="1">SECOND(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A139" ca="1">_xlfn.SEC(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B139">
@@ -5966,7 +5966,7 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A140" ca="1">SECOND({1;2})</f>
+        <f t="array" aca="1" ref="A140" ca="1">_xlfn.SEC({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B140">
@@ -5986,20 +5986,20 @@
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A141" t="e" cm="1">
-        <f t="array" ref="A141">SERIESSUM(D!B1:B2,0,2,D!AR1:AR4)</f>
+      <c r="A141" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A141" ca="1">_xlfn.SECH(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B141">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>9</v>
       </c>
       <c r="C141">
-        <f t="shared" si="7"/>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="D141" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="E141" t="s">
@@ -6008,7 +6008,7 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A142" ca="1">SERIESSUM({1;2},0,2,D!AR1:AR4)</f>
+        <f t="array" aca="1" ref="A142" ca="1">_xlfn.SECH({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B142">
@@ -6028,20 +6028,20 @@
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A143" t="e" cm="1">
-        <f t="array" ref="A143">SERIESSUM(0.785398163,D!B1:B2,2,D!AR1:AR4)</f>
+      <c r="A143" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A143" ca="1">SECOND(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B143">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>9</v>
       </c>
       <c r="C143">
-        <f t="shared" si="7"/>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="D143" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="E143" t="s">
@@ -6050,7 +6050,7 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A144" ca="1">SERIESSUM(0.785398163,{1;2},2,D!AR1:AR4)</f>
+        <f t="array" aca="1" ref="A144" ca="1">SECOND({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B144">
@@ -6071,7 +6071,7 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" t="e" cm="1">
-        <f t="array" ref="A145">SERIESSUM(0.785398163,0,D!B1:B2,D!AR1:AR4)</f>
+        <f t="array" ref="A145">SERIESSUM(D!B1:B2,0,2,D!AR1:AR4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B145">
@@ -6092,7 +6092,7 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A146" ca="1">SERIESSUM(0.785398163,0,{1;2},D!AR1:AR4)</f>
+        <f t="array" aca="1" ref="A146" ca="1">SERIESSUM({1;2},0,2,D!AR1:AR4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B146">
@@ -6112,20 +6112,20 @@
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A147" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A147" ca="1">SIGN(D!B1:B2)</f>
+      <c r="A147" t="e" cm="1">
+        <f t="array" ref="A147">SERIESSUM(0.785398163,D!B1:B2,2,D!AR1:AR4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B147">
-        <f t="shared" ca="1" si="6"/>
-        <v>9</v>
+        <f t="shared" si="6"/>
+        <v>3</v>
       </c>
       <c r="C147">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D147" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="E147" t="s">
@@ -6134,7 +6134,7 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A148" ca="1">SIGN({1;2})</f>
+        <f t="array" aca="1" ref="A148" ca="1">SERIESSUM(0.785398163,{1;2},2,D!AR1:AR4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B148">
@@ -6154,20 +6154,20 @@
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A149" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A149" ca="1">SIN(D!B1:B2)</f>
+      <c r="A149" t="e" cm="1">
+        <f t="array" ref="A149">SERIESSUM(0.785398163,0,D!B1:B2,D!AR1:AR4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B149">
-        <f t="shared" ca="1" si="6"/>
-        <v>9</v>
+        <f t="shared" si="6"/>
+        <v>3</v>
       </c>
       <c r="C149">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D149" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="E149" t="s">
@@ -6176,7 +6176,7 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A150" ca="1">SIN({1;2})</f>
+        <f t="array" aca="1" ref="A150" ca="1">SERIESSUM(0.785398163,0,{1;2},D!AR1:AR4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B150">
@@ -6197,7 +6197,7 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A151" ca="1">SINH(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A151" ca="1">SIGN(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B151">
@@ -6218,7 +6218,7 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A152" ca="1">SINH({1;2})</f>
+        <f t="array" aca="1" ref="A152" ca="1">SIGN({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B152">
@@ -6239,7 +6239,7 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A153" ca="1">SLN(D!B1:B2,7500,10)</f>
+        <f t="array" aca="1" ref="A153" ca="1">SIN(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B153">
@@ -6260,7 +6260,7 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A154" ca="1">SLN({1;2},7500,10)</f>
+        <f t="array" aca="1" ref="A154" ca="1">SIN({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B154">
@@ -6281,7 +6281,7 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A155" ca="1">SLN(30000,D!B1:B2,10)</f>
+        <f t="array" aca="1" ref="A155" ca="1">SINH(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B155">
@@ -6302,7 +6302,7 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A156" ca="1">SLN(30000,{1;2},10)</f>
+        <f t="array" aca="1" ref="A156" ca="1">SINH({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B156">
@@ -6323,7 +6323,7 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A157" ca="1">SLN(30000,7500,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A157" ca="1">SLN(D!B1:B2,7500,10)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B157">
@@ -6344,7 +6344,7 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A158" ca="1">SLN(30000,7500,{1;2})</f>
+        <f t="array" aca="1" ref="A158" ca="1">SLN({1;2},7500,10)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B158">
@@ -6365,7 +6365,7 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A159" ca="1">SMALL(D!B1:B8,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A159" ca="1">SLN(30000,D!B1:B2,10)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B159">
@@ -6386,7 +6386,7 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A160" ca="1">SMALL(D!B1:B8,{1;2})</f>
+        <f t="array" aca="1" ref="A160" ca="1">SLN(30000,{1;2},10)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B160">
@@ -6407,7 +6407,7 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A161" ca="1">SQRT(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A161" ca="1">SLN(30000,7500,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B161">
@@ -6428,7 +6428,7 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A162" ca="1">SQRT({1;2})</f>
+        <f t="array" aca="1" ref="A162" ca="1">SLN(30000,7500,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B162">
@@ -6448,104 +6448,104 @@
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A163" t="e" cm="1">
-        <f t="array" ref="A163">SQRTPI(D!B1:B2)</f>
+      <c r="A163" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A163" ca="1">SMALL(D!B1:B8,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B163">
+        <f t="shared" ca="1" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="C163">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D163" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="E163" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A164" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A164" ca="1">SMALL(D!B1:B8,{1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B164">
+        <f t="shared" ca="1" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="C164">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D164" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="E164" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A165" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A165" ca="1">SQRT(D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B165">
+        <f t="shared" ca="1" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="C165">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D165" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="E165" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A166" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A166" ca="1">SQRT({1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B166">
+        <f t="shared" ca="1" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="C166">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D166" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="E166" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A167" t="e" cm="1">
+        <f t="array" ref="A167">SQRTPI(D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B167">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="C163">
+      <c r="C167">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="D163" t="str">
+      <c r="D167" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="E163" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A164" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A164" ca="1">SQRTPI({1;2})</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B164">
-        <f t="shared" ca="1" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="C164">
-        <f t="shared" ca="1" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="D164" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="E164" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A165" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A165" ca="1">STANDARDIZE(D!B1:B2,40,1.5)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B165">
-        <f t="shared" ca="1" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="C165">
-        <f t="shared" ca="1" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="D165" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="E165" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A166" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A166" ca="1">STANDARDIZE({1;2},40,1.5)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B166">
-        <f t="shared" ca="1" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="C166">
-        <f t="shared" ca="1" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="D166" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="E166" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A167" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A167" ca="1">STANDARDIZE(42,D!B1:B2,1.5)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B167">
-        <f t="shared" ca="1" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="C167">
-        <f t="shared" ca="1" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="D167" t="str">
-        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="E167" t="s">
@@ -6554,7 +6554,7 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A168" ca="1">STANDARDIZE(42,{1;2},1.5)</f>
+        <f t="array" aca="1" ref="A168" ca="1">SQRTPI({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B168">
@@ -6575,7 +6575,7 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A169" ca="1">STANDARDIZE(42,40,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A169" ca="1">STANDARDIZE(D!B1:B2,40,1.5)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B169">
@@ -6596,7 +6596,7 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A170" ca="1">STANDARDIZE(42,40,{1;2})</f>
+        <f t="array" aca="1" ref="A170" ca="1">STANDARDIZE({1;2},40,1.5)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B170">
@@ -6616,209 +6616,209 @@
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A171" cm="1">
-        <f t="array" ref="A171">STDEV(D!B1:B2,2,3)</f>
+      <c r="A171" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A171" ca="1">STANDARDIZE(42,D!B1:B2,1.5)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B171">
+        <f t="shared" ca="1" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="C171">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D171" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="E171" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A172" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A172" ca="1">STANDARDIZE(42,{1;2},1.5)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B172">
+        <f t="shared" ca="1" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="C172">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D172" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="E172" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A173" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A173" ca="1">STANDARDIZE(42,40,D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B173">
+        <f t="shared" ca="1" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="C173">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D173" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="E173" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A174" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A174" ca="1">STANDARDIZE(42,40,{1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B174">
+        <f t="shared" ca="1" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="C174">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D174" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="E174" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A175" cm="1">
+        <f t="array" ref="A175">STDEV(D!B1:B2,2,3)</f>
         <v>2.6299556396765835</v>
       </c>
-      <c r="B171">
+      <c r="B175">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="C171">
+      <c r="C175">
         <f t="shared" si="7"/>
         <v>2.6299556396765835</v>
       </c>
-      <c r="D171" t="str">
+      <c r="D175" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="E171" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A172" cm="1">
-        <f t="array" ref="A172">STDEV({1;2},2,3)</f>
+      <c r="E175" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A176" cm="1">
+        <f t="array" ref="A176">STDEV({1;2},2,3)</f>
         <v>0.81649658092772603</v>
       </c>
-      <c r="B172">
+      <c r="B176">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="C172">
+      <c r="C176">
         <f t="shared" si="7"/>
         <v>0.81649658092772603</v>
       </c>
-      <c r="D172" t="str">
+      <c r="D176" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="E172" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A173" cm="1">
-        <f t="array" ref="A173">STDEV(1,D!B1:B2,3)</f>
+      <c r="E176" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A177" cm="1">
+        <f t="array" ref="A177">STDEV(1,D!B1:B2,3)</f>
         <v>2.9439202887759488</v>
       </c>
-      <c r="B173">
+      <c r="B177">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="C173">
+      <c r="C177">
         <f t="shared" si="7"/>
         <v>2.9439202887759488</v>
       </c>
-      <c r="D173" t="str">
+      <c r="D177" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="E173" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A174" cm="1">
-        <f t="array" ref="A174">STDEV(1,{1;2},3)</f>
+      <c r="E177" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A178" cm="1">
+        <f t="array" ref="A178">STDEV(1,{1;2},3)</f>
         <v>0.9574271077563381</v>
       </c>
-      <c r="B174">
+      <c r="B178">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="C174">
+      <c r="C178">
         <f t="shared" si="7"/>
         <v>0.9574271077563381</v>
       </c>
-      <c r="D174" t="str">
+      <c r="D178" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="E174" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A175" cm="1">
-        <f t="array" ref="A175">STDEV(1,2,D!B1:B2)</f>
+      <c r="E178" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A179" cm="1">
+        <f t="array" ref="A179">STDEV(1,2,D!B1:B2)</f>
         <v>3.0956959368344519</v>
       </c>
-      <c r="B175">
+      <c r="B179">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="C175">
+      <c r="C179">
         <f t="shared" si="7"/>
         <v>3.0956959368344519</v>
       </c>
-      <c r="D175" t="str">
+      <c r="D179" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="E175" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A176" cm="1">
-        <f t="array" ref="A176">STDEV(1,2,{1;2})</f>
+      <c r="E179" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A180" cm="1">
+        <f t="array" ref="A180">STDEV(1,2,{1;2})</f>
         <v>0.57735026918962573</v>
       </c>
-      <c r="B176">
+      <c r="B180">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="C176">
+      <c r="C180">
         <f t="shared" si="7"/>
         <v>0.57735026918962573</v>
       </c>
-      <c r="D176" t="str">
+      <c r="D180" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="E176" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A177" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A177" ca="1">SUBSTITUTE(D!B1:B2,"Sales","Cost")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B177">
-        <f t="shared" ca="1" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="C177">
-        <f t="shared" ca="1" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="D177" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="E177" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A178" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A178" ca="1">SUBSTITUTE({1;2},"Sales","Cost")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B178">
-        <f t="shared" ca="1" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="C178">
-        <f t="shared" ca="1" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="D178" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="E178" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A179" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A179" ca="1">SUBSTITUTE("Sales Data",D!B1:B2,"Cost")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B179">
-        <f t="shared" ca="1" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="C179">
-        <f t="shared" ca="1" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="D179" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="E179" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A180" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A180" ca="1">SUBSTITUTE("Sales Data",{1;2},"Cost")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B180">
-        <f t="shared" ca="1" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="C180">
-        <f t="shared" ca="1" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="D180" t="str">
-        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="E180" t="s">
@@ -6827,7 +6827,7 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A181" ca="1">SUBSTITUTE("Sales Data","Sales",D!B1:B2)</f>
+        <f t="array" aca="1" ref="A181" ca="1">SUBSTITUTE(D!B1:B2,"Sales","Cost")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B181">
@@ -6848,7 +6848,7 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A182" ca="1">SUBSTITUTE("Sales Data","Sales",{1;2})</f>
+        <f t="array" aca="1" ref="A182" ca="1">SUBSTITUTE({1;2},"Sales","Cost")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B182">
@@ -6869,7 +6869,7 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A183" ca="1">SUBTOTAL(D!B1:B2,D!B1:B8)</f>
+        <f t="array" aca="1" ref="A183" ca="1">SUBSTITUTE("Sales Data",D!B1:B2,"Cost")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B183">
@@ -6890,7 +6890,7 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A184" ca="1">SUBTOTAL({1;2},D!B1:B8)</f>
+        <f t="array" aca="1" ref="A184" ca="1">SUBSTITUTE("Sales Data",{1;2},"Cost")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B184">
@@ -6911,7 +6911,7 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A185" ca="1">SUMIF(D!G1:G7,D!B1:B2,D!G1:G7)</f>
+        <f t="array" aca="1" ref="A185" ca="1">SUBSTITUTE("Sales Data","Sales",D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B185">
@@ -6932,7 +6932,7 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A186" ca="1">SUMIF(D!G1:G7,{1;2},D!G1:G7)</f>
+        <f t="array" aca="1" ref="A186" ca="1">SUBSTITUTE("Sales Data","Sales",{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B186">
@@ -6953,7 +6953,7 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A187" ca="1">SUMIFS(D!G1:G7,D!G1:G7,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A187" ca="1">SUBTOTAL(D!B1:B2,D!B1:B8)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B187">
@@ -6974,7 +6974,7 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A188" ca="1">SUMIFS(D!G1:G7,D!G1:G7,{1;2})</f>
+        <f t="array" aca="1" ref="A188" ca="1">SUBTOTAL({1;2},D!B1:B8)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B188">
@@ -6994,20 +6994,20 @@
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A189" cm="1">
-        <f t="array" ref="A189">SUMSQ(D!B1:B2,4)</f>
-        <v>96</v>
+      <c r="A189" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A189" ca="1">SUMIF(D!G1:G7,D!B1:B2,D!G1:G7)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="B189">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>9</v>
       </c>
       <c r="C189">
-        <f t="shared" si="7"/>
-        <v>96</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
       </c>
       <c r="D189" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="E189" t="s">
@@ -7015,20 +7015,20 @@
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A190" cm="1">
-        <f t="array" ref="A190">SUMSQ({1;2},4)</f>
-        <v>21</v>
+      <c r="A190" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A190" ca="1">SUMIF(D!G1:G7,{1;2},D!G1:G7)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="B190">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>9</v>
       </c>
       <c r="C190">
-        <f t="shared" si="7"/>
-        <v>21</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
       </c>
       <c r="D190" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="E190" t="s">
@@ -7036,20 +7036,20 @@
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A191" cm="1">
-        <f t="array" ref="A191">SUMSQ(3,D!B1:B2)</f>
-        <v>89</v>
+      <c r="A191" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A191" ca="1">SUMIFS(D!G1:G7,D!G1:G7,D!B1:B2)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="B191">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>9</v>
       </c>
       <c r="C191">
-        <f t="shared" si="7"/>
-        <v>89</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
       </c>
       <c r="D191" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="E191" t="s">
@@ -7057,20 +7057,20 @@
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A192" cm="1">
-        <f t="array" ref="A192">SUMSQ(3,{1;2})</f>
-        <v>14</v>
+      <c r="A192" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A192" ca="1">SUMIFS(D!G1:G7,D!G1:G7,{1;2})</f>
+        <v>#VALUE!</v>
       </c>
       <c r="B192">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>9</v>
       </c>
       <c r="C192">
-        <f t="shared" si="7"/>
-        <v>14</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
       </c>
       <c r="D192" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="E192" t="s">
@@ -7078,20 +7078,20 @@
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A193" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A193" ca="1">_xlfn.SWITCH(D!B1:B2,1,"one",2,"two","other")</f>
-        <v>#VALUE!</v>
+      <c r="A193" cm="1">
+        <f t="array" ref="A193">SUMSQ(D!B1:B2,4)</f>
+        <v>96</v>
       </c>
       <c r="B193">
-        <f t="shared" ref="B193:B256" ca="1" si="9">IF(ISERROR(A193),ERROR.TYPE(A193),IF(ISNUMBER(A193),0,IF(ISLOGICAL(A193),IF(A193,-1,-2),IF(ISTEXT(A193),-3,-4))))</f>
-        <v>9</v>
+        <f t="shared" ref="B193:B256" si="9">IF(ISERROR(A193),ERROR.TYPE(A193),IF(ISNUMBER(A193),0,IF(ISLOGICAL(A193),IF(A193,-1,-2),IF(ISTEXT(A193),-3,-4))))</f>
+        <v>0</v>
       </c>
       <c r="C193">
-        <f t="shared" ref="C193:C256" ca="1" si="10">IF(ISNUMBER(A193),A193,0)</f>
-        <v>0</v>
+        <f t="shared" ref="C193:C256" si="10">IF(ISNUMBER(A193),A193,0)</f>
+        <v>96</v>
       </c>
       <c r="D193" t="str">
-        <f t="shared" ref="D193:D256" ca="1" si="11">IF(ISTEXT(A193),A193,"")</f>
+        <f t="shared" ref="D193:D256" si="11">IF(ISTEXT(A193),A193,"")</f>
         <v/>
       </c>
       <c r="E193" t="s">
@@ -7099,20 +7099,20 @@
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A194" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A194" ca="1">_xlfn.SWITCH({1;2},1,"one",2,"two","other")</f>
-        <v>#VALUE!</v>
+      <c r="A194" cm="1">
+        <f t="array" ref="A194">SUMSQ({1;2},4)</f>
+        <v>21</v>
       </c>
       <c r="B194">
-        <f t="shared" ca="1" si="9"/>
-        <v>9</v>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="C194">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>21</v>
       </c>
       <c r="D194" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="E194" t="s">
@@ -7120,20 +7120,20 @@
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A195" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A195" ca="1">_xlfn.SWITCH(2,D!B1:B2,"one",2,"two","other")</f>
-        <v>#VALUE!</v>
+      <c r="A195" cm="1">
+        <f t="array" ref="A195">SUMSQ(3,D!B1:B2)</f>
+        <v>89</v>
       </c>
       <c r="B195">
-        <f t="shared" ca="1" si="9"/>
-        <v>9</v>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="C195">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>89</v>
       </c>
       <c r="D195" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="E195" t="s">
@@ -7141,20 +7141,20 @@
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A196" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A196" ca="1">_xlfn.SWITCH(2,{1;2},"one",2,"two","other")</f>
-        <v>#VALUE!</v>
+      <c r="A196" cm="1">
+        <f t="array" ref="A196">SUMSQ(3,{1;2})</f>
+        <v>14</v>
       </c>
       <c r="B196">
-        <f t="shared" ca="1" si="9"/>
-        <v>9</v>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="C196">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>14</v>
       </c>
       <c r="D196" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="E196" t="s">
@@ -7162,260 +7162,260 @@
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A197" t="str" cm="1">
-        <f t="array" ref="A197">_xlfn.SWITCH(2,1,D!B1:B2,2,"two","other")</f>
+      <c r="A197" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A197" ca="1">_xlfn.SWITCH(D!B1:B2,1,"one",2,"two","other")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B197">
+        <f t="shared" ca="1" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="C197">
+        <f t="shared" ca="1" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="D197" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="E197" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A198" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A198" ca="1">_xlfn.SWITCH({1;2},1,"one",2,"two","other")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B198">
+        <f t="shared" ca="1" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="C198">
+        <f t="shared" ca="1" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="D198" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="E198" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A199" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A199" ca="1">_xlfn.SWITCH(2,D!B1:B2,"one",2,"two","other")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B199">
+        <f t="shared" ca="1" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="C199">
+        <f t="shared" ca="1" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="D199" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="E199" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A200" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A200" ca="1">_xlfn.SWITCH(2,{1;2},"one",2,"two","other")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B200">
+        <f t="shared" ca="1" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="C200">
+        <f t="shared" ca="1" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="D200" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="E200" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A201" t="str" cm="1">
+        <f t="array" ref="A201">_xlfn.SWITCH(2,1,D!B1:B2,2,"two","other")</f>
         <v>two</v>
       </c>
-      <c r="B197">
+      <c r="B201">
         <f t="shared" si="9"/>
         <v>-3</v>
       </c>
-      <c r="C197">
+      <c r="C201">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="D197" t="str">
+      <c r="D201" t="str">
         <f t="shared" si="11"/>
         <v>two</v>
       </c>
-      <c r="E197" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A198" t="str" cm="1">
-        <f t="array" ref="A198">_xlfn.SWITCH(2,1,{1;2},2,"two","other")</f>
+      <c r="E201" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A202" t="str" cm="1">
+        <f t="array" ref="A202">_xlfn.SWITCH(2,1,{1;2},2,"two","other")</f>
         <v>two</v>
       </c>
-      <c r="B198">
+      <c r="B202">
         <f t="shared" si="9"/>
         <v>-3</v>
       </c>
-      <c r="C198">
+      <c r="C202">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="D198" t="str">
+      <c r="D202" t="str">
         <f t="shared" si="11"/>
         <v>two</v>
       </c>
-      <c r="E198" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A199" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A199" ca="1">_xlfn.SWITCH(2,1,"one",D!B1:B2,"two","other")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B199">
-        <f t="shared" ca="1" si="9"/>
-        <v>9</v>
-      </c>
-      <c r="C199">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="D199" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="E199" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A200" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A200" ca="1">_xlfn.SWITCH(2,1,"one",{1;2},"two","other")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B200">
-        <f t="shared" ca="1" si="9"/>
-        <v>9</v>
-      </c>
-      <c r="C200">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="D200" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="E200" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A201" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A201" ca="1">_xlfn.SWITCH(2,1,"one",2,D!B1:B2,"other")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B201">
-        <f t="shared" ca="1" si="9"/>
-        <v>9</v>
-      </c>
-      <c r="C201">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="D201" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="E201" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A202" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A202" ca="1">_xlfn.SWITCH(2,1,"one",2,{1;2},"other")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B202">
-        <f t="shared" ca="1" si="9"/>
-        <v>9</v>
-      </c>
-      <c r="C202">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="D202" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
       <c r="E202" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A203" t="str" cm="1">
-        <f t="array" ref="A203">_xlfn.SWITCH(2,1,"one",2,"two",D!B1:B2)</f>
+      <c r="A203" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A203" ca="1">_xlfn.SWITCH(2,1,"one",D!B1:B2,"two","other")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B203">
+        <f t="shared" ca="1" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="C203">
+        <f t="shared" ca="1" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="D203" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="E203" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A204" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A204" ca="1">_xlfn.SWITCH(2,1,"one",{1;2},"two","other")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B204">
+        <f t="shared" ca="1" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="C204">
+        <f t="shared" ca="1" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="D204" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="E204" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A205" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A205" ca="1">_xlfn.SWITCH(2,1,"one",2,D!B1:B2,"other")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B205">
+        <f t="shared" ca="1" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="C205">
+        <f t="shared" ca="1" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="D205" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="E205" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A206" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A206" ca="1">_xlfn.SWITCH(2,1,"one",2,{1;2},"other")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B206">
+        <f t="shared" ca="1" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="C206">
+        <f t="shared" ca="1" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="D206" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="E206" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A207" t="str" cm="1">
+        <f t="array" ref="A207">_xlfn.SWITCH(2,1,"one",2,"two",D!B1:B2)</f>
         <v>two</v>
       </c>
-      <c r="B203">
+      <c r="B207">
         <f t="shared" si="9"/>
         <v>-3</v>
       </c>
-      <c r="C203">
+      <c r="C207">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="D203" t="str">
+      <c r="D207" t="str">
         <f t="shared" si="11"/>
         <v>two</v>
       </c>
-      <c r="E203" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A204" t="str" cm="1">
-        <f t="array" ref="A204">_xlfn.SWITCH(2,1,"one",2,"two",{1;2})</f>
+      <c r="E207" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A208" t="str" cm="1">
+        <f t="array" ref="A208">_xlfn.SWITCH(2,1,"one",2,"two",{1;2})</f>
         <v>two</v>
       </c>
-      <c r="B204">
+      <c r="B208">
         <f t="shared" si="9"/>
         <v>-3</v>
       </c>
-      <c r="C204">
+      <c r="C208">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="D204" t="str">
+      <c r="D208" t="str">
         <f t="shared" si="11"/>
         <v>two</v>
       </c>
-      <c r="E204" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A205" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A205" ca="1">SYD(D!B1:B2,7500,10,1)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B205">
-        <f t="shared" ca="1" si="9"/>
-        <v>9</v>
-      </c>
-      <c r="C205">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="D205" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="E205" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A206" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A206" ca="1">SYD({1;2},7500,10,1)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B206">
-        <f t="shared" ca="1" si="9"/>
-        <v>9</v>
-      </c>
-      <c r="C206">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="D206" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="E206" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A207" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A207" ca="1">SYD(30000,D!B1:B2,10,1)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B207">
-        <f t="shared" ca="1" si="9"/>
-        <v>9</v>
-      </c>
-      <c r="C207">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="D207" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="E207" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A208" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A208" ca="1">SYD(30000,{1;2},10,1)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B208">
-        <f t="shared" ca="1" si="9"/>
-        <v>9</v>
-      </c>
-      <c r="C208">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="D208" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
       <c r="E208" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A209" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A209" ca="1">SYD(30000,7500,D!B1:B2,1)</f>
+        <f t="array" aca="1" ref="A209" ca="1">SYD(D!B1:B2,7500,10,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B209">
@@ -7436,7 +7436,7 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A210" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A210" ca="1">SYD(30000,7500,{1;2},1)</f>
+        <f t="array" aca="1" ref="A210" ca="1">SYD({1;2},7500,10,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B210">
@@ -7457,7 +7457,7 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A211" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A211" ca="1">SYD(30000,7500,10,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A211" ca="1">SYD(30000,D!B1:B2,10,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B211">
@@ -7478,7 +7478,7 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A212" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A212" ca="1">SYD(30000,7500,10,{1;2})</f>
+        <f t="array" aca="1" ref="A212" ca="1">SYD(30000,{1;2},10,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B212">
@@ -7498,104 +7498,104 @@
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A213" t="str" cm="1">
-        <f t="array" ref="A213">T(D!B1:B2)</f>
-        <v/>
+      <c r="A213" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A213" ca="1">SYD(30000,7500,D!B1:B2,1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="B213">
+        <f t="shared" ca="1" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="C213">
+        <f t="shared" ca="1" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="D213" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="E213" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A214" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A214" ca="1">SYD(30000,7500,{1;2},1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B214">
+        <f t="shared" ca="1" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="C214">
+        <f t="shared" ca="1" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="D214" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="E214" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A215" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A215" ca="1">SYD(30000,7500,10,D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B215">
+        <f t="shared" ca="1" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="C215">
+        <f t="shared" ca="1" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="D215" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="E215" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A216" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A216" ca="1">SYD(30000,7500,10,{1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B216">
+        <f t="shared" ca="1" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="C216">
+        <f t="shared" ca="1" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="D216" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="E216" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A217" t="str" cm="1">
+        <f t="array" ref="A217">T(D!B1:B2)</f>
+        <v/>
+      </c>
+      <c r="B217">
         <f t="shared" si="9"/>
         <v>-3</v>
       </c>
-      <c r="C213">
+      <c r="C217">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="D213" t="str">
+      <c r="D217" t="str">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="E213" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A214" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A214" ca="1">T({1;2})</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B214">
-        <f t="shared" ca="1" si="9"/>
-        <v>9</v>
-      </c>
-      <c r="C214">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="D214" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="E214" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A215" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A215" ca="1">_xlfn.T.DIST(D!B1:B2,1,TRUE)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B215">
-        <f t="shared" ca="1" si="9"/>
-        <v>9</v>
-      </c>
-      <c r="C215">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="D215" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="E215" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A216" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A216" ca="1">_xlfn.T.DIST({1;2},1,TRUE)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B216">
-        <f t="shared" ca="1" si="9"/>
-        <v>9</v>
-      </c>
-      <c r="C216">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="D216" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="E216" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A217" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A217" ca="1">_xlfn.T.DIST(60,D!B1:B2,TRUE)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B217">
-        <f t="shared" ca="1" si="9"/>
-        <v>9</v>
-      </c>
-      <c r="C217">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="D217" t="str">
-        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="E217" t="s">
@@ -7604,7 +7604,7 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A218" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A218" ca="1">_xlfn.T.DIST(60,{1;2},TRUE)</f>
+        <f t="array" aca="1" ref="A218" ca="1">T({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B218">
@@ -7625,7 +7625,7 @@
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A219" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A219" ca="1">_xlfn.T.DIST(60,1,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A219" ca="1">_xlfn.T.DIST(D!B1:B2,1,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B219">
@@ -7646,7 +7646,7 @@
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A220" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A220" ca="1">_xlfn.T.DIST(60,1,{1;2})</f>
+        <f t="array" aca="1" ref="A220" ca="1">_xlfn.T.DIST({1;2},1,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B220">
@@ -7667,7 +7667,7 @@
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A221" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A221" ca="1">_xlfn.T.DIST.2T(D!B1:B2,60)</f>
+        <f t="array" aca="1" ref="A221" ca="1">_xlfn.T.DIST(60,D!B1:B2,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B221">
@@ -7688,7 +7688,7 @@
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A222" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A222" ca="1">_xlfn.T.DIST.2T({1;2},60)</f>
+        <f t="array" aca="1" ref="A222" ca="1">_xlfn.T.DIST(60,{1;2},TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B222">
@@ -7709,7 +7709,7 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A223" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A223" ca="1">_xlfn.T.DIST.2T(1.959999998,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A223" ca="1">_xlfn.T.DIST(60,1,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B223">
@@ -7730,7 +7730,7 @@
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A224" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A224" ca="1">_xlfn.T.DIST.2T(1.959999998,{1;2})</f>
+        <f t="array" aca="1" ref="A224" ca="1">_xlfn.T.DIST(60,1,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B224">
@@ -7751,7 +7751,7 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A225" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A225" ca="1">_xlfn.T.DIST.RT(D!B1:B2,60)</f>
+        <f t="array" aca="1" ref="A225" ca="1">_xlfn.T.DIST.2T(D!B1:B2,60)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B225">
@@ -7772,7 +7772,7 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A226" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A226" ca="1">_xlfn.T.DIST.RT({1;2},60)</f>
+        <f t="array" aca="1" ref="A226" ca="1">_xlfn.T.DIST.2T({1;2},60)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B226">
@@ -7793,7 +7793,7 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A227" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A227" ca="1">_xlfn.T.DIST.RT(1.959999998,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A227" ca="1">_xlfn.T.DIST.2T(1.959999998,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B227">
@@ -7814,7 +7814,7 @@
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A228" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A228" ca="1">_xlfn.T.DIST.RT(1.959999998,{1;2})</f>
+        <f t="array" aca="1" ref="A228" ca="1">_xlfn.T.DIST.2T(1.959999998,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B228">
@@ -7835,7 +7835,7 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A229" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A229" ca="1">_xlfn.T.INV(D!B1:B2,2)</f>
+        <f t="array" aca="1" ref="A229" ca="1">_xlfn.T.DIST.RT(D!B1:B2,60)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B229">
@@ -7856,7 +7856,7 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A230" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A230" ca="1">_xlfn.T.INV({1;2},2)</f>
+        <f t="array" aca="1" ref="A230" ca="1">_xlfn.T.DIST.RT({1;2},60)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B230">
@@ -7877,7 +7877,7 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A231" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A231" ca="1">_xlfn.T.INV(0.75,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A231" ca="1">_xlfn.T.DIST.RT(1.959999998,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B231">
@@ -7898,7 +7898,7 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A232" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A232" ca="1">_xlfn.T.INV(0.75,{1;2})</f>
+        <f t="array" aca="1" ref="A232" ca="1">_xlfn.T.DIST.RT(1.959999998,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B232">
@@ -7919,7 +7919,7 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A233" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A233" ca="1">_xlfn.T.INV.2T(D!B1:B2,60)</f>
+        <f t="array" aca="1" ref="A233" ca="1">_xlfn.T.INV(D!B1:B2,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B233">
@@ -7940,7 +7940,7 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A234" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A234" ca="1">_xlfn.T.INV.2T({1;2},60)</f>
+        <f t="array" aca="1" ref="A234" ca="1">_xlfn.T.INV({1;2},2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B234">
@@ -7961,7 +7961,7 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A235" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A235" ca="1">_xlfn.T.INV.2T(0.546449,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A235" ca="1">_xlfn.T.INV(0.75,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B235">
@@ -7982,7 +7982,7 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A236" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A236" ca="1">_xlfn.T.INV.2T(0.546449,{1;2})</f>
+        <f t="array" aca="1" ref="A236" ca="1">_xlfn.T.INV(0.75,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B236">
@@ -8003,7 +8003,7 @@
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A237" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A237" ca="1">_xlfn.T.TEST(D!B1:B8,D!C1:C8,D!B1:B2,1)</f>
+        <f t="array" aca="1" ref="A237" ca="1">_xlfn.T.INV.2T(D!B1:B2,60)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B237">
@@ -8024,7 +8024,7 @@
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A238" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A238" ca="1">_xlfn.T.TEST(D!B1:B8,D!C1:C8,{1;2},1)</f>
+        <f t="array" aca="1" ref="A238" ca="1">_xlfn.T.INV.2T({1;2},60)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B238">
@@ -8045,7 +8045,7 @@
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A239" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A239" ca="1">_xlfn.T.TEST(D!B1:B8,D!C1:C8,2,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A239" ca="1">_xlfn.T.INV.2T(0.546449,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B239">
@@ -8066,7 +8066,7 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A240" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A240" ca="1">_xlfn.T.TEST(D!B1:B8,D!C1:C8,2,{1;2})</f>
+        <f t="array" aca="1" ref="A240" ca="1">_xlfn.T.INV.2T(0.546449,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B240">
@@ -8087,7 +8087,7 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A241" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A241" ca="1">TAN(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A241" ca="1">_xlfn.T.TEST(D!B1:B8,D!C1:C8,D!B1:B2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B241">
@@ -8108,7 +8108,7 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A242" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A242" ca="1">TAN({1;2})</f>
+        <f t="array" aca="1" ref="A242" ca="1">_xlfn.T.TEST(D!B1:B8,D!C1:C8,{1;2},1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B242">
@@ -8129,7 +8129,7 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A243" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A243" ca="1">TANH(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A243" ca="1">_xlfn.T.TEST(D!B1:B8,D!C1:C8,2,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B243">
@@ -8150,7 +8150,7 @@
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A244" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A244" ca="1">TANH({1;2})</f>
+        <f t="array" aca="1" ref="A244" ca="1">_xlfn.T.TEST(D!B1:B8,D!C1:C8,2,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B244">
@@ -8170,20 +8170,20 @@
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A245" t="e" cm="1">
-        <f t="array" ref="A245">TBILLEQ(D!B1:B2,39600,0.0914)</f>
+      <c r="A245" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A245" ca="1">TAN(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B245">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>9</v>
       </c>
       <c r="C245">
-        <f t="shared" si="10"/>
+        <f t="shared" ca="1" si="10"/>
         <v>0</v>
       </c>
       <c r="D245" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="E245" t="s">
@@ -8192,7 +8192,7 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A246" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A246" ca="1">TBILLEQ({1;2},39600,0.0914)</f>
+        <f t="array" aca="1" ref="A246" ca="1">TAN({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B246">
@@ -8212,20 +8212,20 @@
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A247" t="e" cm="1">
-        <f t="array" ref="A247">TBILLEQ(39538,D!B1:B2,0.0914)</f>
+      <c r="A247" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A247" ca="1">TANH(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B247">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>9</v>
       </c>
       <c r="C247">
-        <f t="shared" si="10"/>
+        <f t="shared" ca="1" si="10"/>
         <v>0</v>
       </c>
       <c r="D247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="E247" t="s">
@@ -8234,7 +8234,7 @@
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A248" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A248" ca="1">TBILLEQ(39538,{1;2},0.0914)</f>
+        <f t="array" aca="1" ref="A248" ca="1">TANH({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B248">
@@ -8255,7 +8255,7 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A249" t="e" cm="1">
-        <f t="array" ref="A249">TBILLEQ(39538,39600,D!B1:B2)</f>
+        <f t="array" ref="A249">TBILLEQ(D!B1:B2,39600,0.0914)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B249">
@@ -8276,7 +8276,7 @@
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A250" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A250" ca="1">TBILLEQ(39538,39600,{1;2})</f>
+        <f t="array" aca="1" ref="A250" ca="1">TBILLEQ({1;2},39600,0.0914)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B250">
@@ -8297,7 +8297,7 @@
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A251" t="e" cm="1">
-        <f t="array" ref="A251">TBILLPRICE(D!B1:B2,39600,0.09)</f>
+        <f t="array" ref="A251">TBILLEQ(39538,D!B1:B2,0.0914)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B251">
@@ -8318,7 +8318,7 @@
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A252" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A252" ca="1">TBILLPRICE({1;2},39600,0.09)</f>
+        <f t="array" aca="1" ref="A252" ca="1">TBILLEQ(39538,{1;2},0.0914)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B252">
@@ -8339,7 +8339,7 @@
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A253" t="e" cm="1">
-        <f t="array" ref="A253">TBILLPRICE(39538,D!B1:B2,0.09)</f>
+        <f t="array" ref="A253">TBILLEQ(39538,39600,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B253">
@@ -8360,7 +8360,7 @@
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A254" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A254" ca="1">TBILLPRICE(39538,{1;2},0.09)</f>
+        <f t="array" aca="1" ref="A254" ca="1">TBILLEQ(39538,39600,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B254">
@@ -8381,7 +8381,7 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A255" t="e" cm="1">
-        <f t="array" ref="A255">TBILLPRICE(39538,39600,D!B1:B2)</f>
+        <f t="array" ref="A255">TBILLPRICE(D!B1:B2,39600,0.09)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B255">
@@ -8402,7 +8402,7 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A256" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A256" ca="1">TBILLPRICE(39538,39600,{1;2})</f>
+        <f t="array" aca="1" ref="A256" ca="1">TBILLPRICE({1;2},39600,0.09)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B256">
@@ -8423,7 +8423,7 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A257" t="e" cm="1">
-        <f t="array" ref="A257">TBILLYIELD(D!B1:B2,39600,98.45)</f>
+        <f t="array" ref="A257">TBILLPRICE(39538,D!B1:B2,0.09)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B257">
@@ -8444,7 +8444,7 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A258" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A258" ca="1">TBILLYIELD({1;2},39600,98.45)</f>
+        <f t="array" aca="1" ref="A258" ca="1">TBILLPRICE(39538,{1;2},0.09)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B258">
@@ -8465,7 +8465,7 @@
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A259" t="e" cm="1">
-        <f t="array" ref="A259">TBILLYIELD(39538,D!B1:B2,98.45)</f>
+        <f t="array" ref="A259">TBILLPRICE(39538,39600,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B259">
@@ -8486,7 +8486,7 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A260" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A260" ca="1">TBILLYIELD(39538,{1;2},98.45)</f>
+        <f t="array" aca="1" ref="A260" ca="1">TBILLPRICE(39538,39600,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B260">
@@ -8507,7 +8507,7 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A261" t="e" cm="1">
-        <f t="array" ref="A261">TBILLYIELD(39538,39600,D!B1:B2)</f>
+        <f t="array" ref="A261">TBILLYIELD(D!B1:B2,39600,98.45)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B261">
@@ -8528,7 +8528,7 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A262" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A262" ca="1">TBILLYIELD(39538,39600,{1;2})</f>
+        <f t="array" aca="1" ref="A262" ca="1">TBILLYIELD({1;2},39600,98.45)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B262">
@@ -8548,20 +8548,20 @@
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A263" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A263" ca="1">TDIST(D!B1:B2,60,2)</f>
+      <c r="A263" t="e" cm="1">
+        <f t="array" ref="A263">TBILLYIELD(39538,D!B1:B2,98.45)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B263">
-        <f t="shared" ca="1" si="12"/>
-        <v>9</v>
+        <f t="shared" si="12"/>
+        <v>3</v>
       </c>
       <c r="C263">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D263" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="E263" t="s">
@@ -8570,7 +8570,7 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A264" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A264" ca="1">TDIST({1;2},60,2)</f>
+        <f t="array" aca="1" ref="A264" ca="1">TBILLYIELD(39538,{1;2},98.45)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B264">
@@ -8590,20 +8590,20 @@
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A265" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A265" ca="1">TDIST(1.959999998,D!B1:B2,2)</f>
+      <c r="A265" t="e" cm="1">
+        <f t="array" ref="A265">TBILLYIELD(39538,39600,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B265">
-        <f t="shared" ca="1" si="12"/>
-        <v>9</v>
+        <f t="shared" si="12"/>
+        <v>3</v>
       </c>
       <c r="C265">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D265" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="E265" t="s">
@@ -8612,7 +8612,7 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A266" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A266" ca="1">TDIST(1.959999998,{1;2},2)</f>
+        <f t="array" aca="1" ref="A266" ca="1">TBILLYIELD(39538,39600,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B266">
@@ -8633,7 +8633,7 @@
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A267" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A267" ca="1">TDIST(1.959999998,60,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A267" ca="1">TDIST(D!B1:B2,60,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B267">
@@ -8654,7 +8654,7 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A268" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A268" ca="1">TDIST(1.959999998,60,{1;2})</f>
+        <f t="array" aca="1" ref="A268" ca="1">TDIST({1;2},60,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B268">
@@ -8675,7 +8675,7 @@
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A269" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A269" ca="1">TEXT(D!B1:B2,"$#,##0.00")</f>
+        <f t="array" aca="1" ref="A269" ca="1">TDIST(1.959999998,D!B1:B2,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B269">
@@ -8696,7 +8696,7 @@
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A270" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A270" ca="1">TEXT({1;2},"$#,##0.00")</f>
+        <f t="array" aca="1" ref="A270" ca="1">TDIST(1.959999998,{1;2},2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B270">
@@ -8717,7 +8717,7 @@
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A271" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A271" ca="1">TEXT(1234.567,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A271" ca="1">TDIST(1.959999998,60,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B271">
@@ -8738,7 +8738,7 @@
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A272" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A272" ca="1">TEXT(1234.567,{1;2})</f>
+        <f t="array" aca="1" ref="A272" ca="1">TDIST(1.959999998,60,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B272">
@@ -8759,7 +8759,7 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A273" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A273" ca="1">_xlfn.TEXTAFTER(D!B1:B2,"-")</f>
+        <f t="array" aca="1" ref="A273" ca="1">TEXT(D!B1:B2,"$#,##0.00")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B273">
@@ -8780,7 +8780,7 @@
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A274" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A274" ca="1">_xlfn.TEXTAFTER({1;2},"-")</f>
+        <f t="array" aca="1" ref="A274" ca="1">TEXT({1;2},"$#,##0.00")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B274">
@@ -8800,20 +8800,20 @@
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A275" t="e" cm="1">
-        <f t="array" ref="A275">_xlfn.TEXTAFTER("a-b-c",D!B1:B2)</f>
-        <v>#N/A</v>
+      <c r="A275" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A275" ca="1">TEXT(1234.567,D!B1:B2)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="B275">
-        <f t="shared" si="12"/>
-        <v>7</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>9</v>
       </c>
       <c r="C275">
-        <f t="shared" si="13"/>
+        <f t="shared" ca="1" si="13"/>
         <v>0</v>
       </c>
       <c r="D275" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="E275" t="s">
@@ -8821,20 +8821,20 @@
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A276" t="e" cm="1">
-        <f t="array" ref="A276">_xlfn.TEXTAFTER("a-b-c",{1;2})</f>
-        <v>#N/A</v>
+      <c r="A276" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A276" ca="1">TEXT(1234.567,{1;2})</f>
+        <v>#VALUE!</v>
       </c>
       <c r="B276">
-        <f t="shared" si="12"/>
-        <v>7</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>9</v>
       </c>
       <c r="C276">
-        <f t="shared" si="13"/>
+        <f t="shared" ca="1" si="13"/>
         <v>0</v>
       </c>
       <c r="D276" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="E276" t="s">
@@ -8843,7 +8843,7 @@
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A277" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A277" ca="1">_xlfn.TEXTBEFORE(D!B1:B2,"-")</f>
+        <f t="array" aca="1" ref="A277" ca="1">_xlfn.TEXTAFTER(D!B1:B2,"-")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B277">
@@ -8864,7 +8864,7 @@
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A278" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A278" ca="1">_xlfn.TEXTBEFORE({1;2},"-")</f>
+        <f t="array" aca="1" ref="A278" ca="1">_xlfn.TEXTAFTER({1;2},"-")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B278">
@@ -8885,7 +8885,7 @@
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A279" t="e" cm="1">
-        <f t="array" ref="A279">_xlfn.TEXTBEFORE("a-b-c",D!B1:B2)</f>
+        <f t="array" ref="A279">_xlfn.TEXTAFTER("a-b-c",D!B1:B2)</f>
         <v>#N/A</v>
       </c>
       <c r="B279">
@@ -8906,7 +8906,7 @@
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A280" t="e" cm="1">
-        <f t="array" ref="A280">_xlfn.TEXTBEFORE("a-b-c",{1;2})</f>
+        <f t="array" ref="A280">_xlfn.TEXTAFTER("a-b-c",{1;2})</f>
         <v>#N/A</v>
       </c>
       <c r="B280">
@@ -8926,62 +8926,62 @@
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A281" t="str" cm="1">
-        <f t="array" ref="A281">_xlfn.TEXTJOIN(D!B1:B2,TRUE,"a","","b")</f>
-        <v>a4b</v>
+      <c r="A281" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A281" ca="1">_xlfn.TEXTBEFORE(D!B1:B2,"-")</f>
+        <v>#VALUE!</v>
       </c>
       <c r="B281">
-        <f t="shared" si="12"/>
-        <v>-3</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>9</v>
       </c>
       <c r="C281">
-        <f t="shared" si="13"/>
+        <f t="shared" ca="1" si="13"/>
         <v>0</v>
       </c>
       <c r="D281" t="str">
-        <f t="shared" si="14"/>
-        <v>a4b</v>
+        <f t="shared" ca="1" si="14"/>
+        <v/>
       </c>
       <c r="E281" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A282" t="str" cm="1">
-        <f t="array" ref="A282">_xlfn.TEXTJOIN({1;2},TRUE,"a","","b")</f>
-        <v>a1b</v>
+      <c r="A282" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A282" ca="1">_xlfn.TEXTBEFORE({1;2},"-")</f>
+        <v>#VALUE!</v>
       </c>
       <c r="B282">
-        <f t="shared" si="12"/>
-        <v>-3</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>9</v>
       </c>
       <c r="C282">
-        <f t="shared" si="13"/>
+        <f t="shared" ca="1" si="13"/>
         <v>0</v>
       </c>
       <c r="D282" t="str">
-        <f t="shared" si="14"/>
-        <v>a1b</v>
+        <f t="shared" ca="1" si="14"/>
+        <v/>
       </c>
       <c r="E282" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A283" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A283" ca="1">_xlfn.TEXTJOIN(", ",D!B1:B2,"a","","b")</f>
-        <v>#VALUE!</v>
+      <c r="A283" t="e" cm="1">
+        <f t="array" ref="A283">_xlfn.TEXTBEFORE("a-b-c",D!B1:B2)</f>
+        <v>#N/A</v>
       </c>
       <c r="B283">
-        <f t="shared" ca="1" si="12"/>
-        <v>9</v>
+        <f t="shared" si="12"/>
+        <v>7</v>
       </c>
       <c r="C283">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D283" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="E283" t="s">
@@ -8989,20 +8989,20 @@
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A284" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A284" ca="1">_xlfn.TEXTJOIN(", ",{1;2},"a","","b")</f>
-        <v>#VALUE!</v>
+      <c r="A284" t="e" cm="1">
+        <f t="array" ref="A284">_xlfn.TEXTBEFORE("a-b-c",{1;2})</f>
+        <v>#N/A</v>
       </c>
       <c r="B284">
-        <f t="shared" ca="1" si="12"/>
-        <v>9</v>
+        <f t="shared" si="12"/>
+        <v>7</v>
       </c>
       <c r="C284">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D284" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="E284" t="s">
@@ -9011,8 +9011,8 @@
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A285" t="str" cm="1">
-        <f t="array" ref="A285">_xlfn.TEXTJOIN(", ",TRUE,D!B1:B2,"","b")</f>
-        <v>4, 8, b</v>
+        <f t="array" ref="A285">_xlfn.TEXTJOIN(D!B1:B2,TRUE,"a","","b")</f>
+        <v>a4b</v>
       </c>
       <c r="B285">
         <f t="shared" si="12"/>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="D285" t="str">
         <f t="shared" si="14"/>
-        <v>4, 8, b</v>
+        <v>a4b</v>
       </c>
       <c r="E285" t="s">
         <v>333</v>
@@ -9032,8 +9032,8 @@
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A286" t="str" cm="1">
-        <f t="array" ref="A286">_xlfn.TEXTJOIN(", ",TRUE,{1;2},"","b")</f>
-        <v>1, 2, b</v>
+        <f t="array" ref="A286">_xlfn.TEXTJOIN({1;2},TRUE,"a","","b")</f>
+        <v>a1b</v>
       </c>
       <c r="B286">
         <f t="shared" si="12"/>
@@ -9045,49 +9045,49 @@
       </c>
       <c r="D286" t="str">
         <f t="shared" si="14"/>
-        <v>1, 2, b</v>
+        <v>a1b</v>
       </c>
       <c r="E286" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A287" t="str" cm="1">
-        <f t="array" ref="A287">_xlfn.TEXTJOIN(", ",TRUE,"a",D!B1:B2,"b")</f>
-        <v>a, 4, 8, b</v>
+      <c r="A287" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A287" ca="1">_xlfn.TEXTJOIN(", ",D!B1:B2,"a","","b")</f>
+        <v>#VALUE!</v>
       </c>
       <c r="B287">
-        <f t="shared" si="12"/>
-        <v>-3</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>9</v>
       </c>
       <c r="C287">
-        <f t="shared" si="13"/>
+        <f t="shared" ca="1" si="13"/>
         <v>0</v>
       </c>
       <c r="D287" t="str">
-        <f t="shared" si="14"/>
-        <v>a, 4, 8, b</v>
+        <f t="shared" ca="1" si="14"/>
+        <v/>
       </c>
       <c r="E287" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A288" t="str" cm="1">
-        <f t="array" ref="A288">_xlfn.TEXTJOIN(", ",TRUE,"a",{1;2},"b")</f>
-        <v>a, 1, 2, b</v>
+      <c r="A288" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A288" ca="1">_xlfn.TEXTJOIN(", ",{1;2},"a","","b")</f>
+        <v>#VALUE!</v>
       </c>
       <c r="B288">
-        <f t="shared" si="12"/>
-        <v>-3</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>9</v>
       </c>
       <c r="C288">
-        <f t="shared" si="13"/>
+        <f t="shared" ca="1" si="13"/>
         <v>0</v>
       </c>
       <c r="D288" t="str">
-        <f t="shared" si="14"/>
-        <v>a, 1, 2, b</v>
+        <f t="shared" ca="1" si="14"/>
+        <v/>
       </c>
       <c r="E288" t="s">
         <v>336</v>
@@ -9095,8 +9095,8 @@
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A289" t="str" cm="1">
-        <f t="array" ref="A289">_xlfn.TEXTJOIN(", ",TRUE,"a","",D!B1:B2)</f>
-        <v>a, 4, 8</v>
+        <f t="array" ref="A289">_xlfn.TEXTJOIN(", ",TRUE,D!B1:B2,"","b")</f>
+        <v>4, 8, b</v>
       </c>
       <c r="B289">
         <f t="shared" si="12"/>
@@ -9108,7 +9108,7 @@
       </c>
       <c r="D289" t="str">
         <f t="shared" si="14"/>
-        <v>a, 4, 8</v>
+        <v>4, 8, b</v>
       </c>
       <c r="E289" t="s">
         <v>337</v>
@@ -9116,8 +9116,8 @@
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A290" t="str" cm="1">
-        <f t="array" ref="A290">_xlfn.TEXTJOIN(", ",TRUE,"a","",{1;2})</f>
-        <v>a, 1, 2</v>
+        <f t="array" ref="A290">_xlfn.TEXTJOIN(", ",TRUE,{1;2},"","b")</f>
+        <v>1, 2, b</v>
       </c>
       <c r="B290">
         <f t="shared" si="12"/>
@@ -9129,91 +9129,91 @@
       </c>
       <c r="D290" t="str">
         <f t="shared" si="14"/>
-        <v>a, 1, 2</v>
+        <v>1, 2, b</v>
       </c>
       <c r="E290" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A291" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A291" ca="1">TIME(D!B1:B2,0,0)</f>
-        <v>#VALUE!</v>
+      <c r="A291" t="str" cm="1">
+        <f t="array" ref="A291">_xlfn.TEXTJOIN(", ",TRUE,"a",D!B1:B2,"b")</f>
+        <v>a, 4, 8, b</v>
       </c>
       <c r="B291">
-        <f t="shared" ca="1" si="12"/>
-        <v>9</v>
+        <f t="shared" si="12"/>
+        <v>-3</v>
       </c>
       <c r="C291">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D291" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
+        <f t="shared" si="14"/>
+        <v>a, 4, 8, b</v>
       </c>
       <c r="E291" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A292" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A292" ca="1">TIME({1;2},0,0)</f>
-        <v>#VALUE!</v>
+      <c r="A292" t="str" cm="1">
+        <f t="array" ref="A292">_xlfn.TEXTJOIN(", ",TRUE,"a",{1;2},"b")</f>
+        <v>a, 1, 2, b</v>
       </c>
       <c r="B292">
-        <f t="shared" ca="1" si="12"/>
-        <v>9</v>
+        <f t="shared" si="12"/>
+        <v>-3</v>
       </c>
       <c r="C292">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D292" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
+        <f t="shared" si="14"/>
+        <v>a, 1, 2, b</v>
       </c>
       <c r="E292" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A293" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A293" ca="1">TIME(12,D!B1:B2,0)</f>
-        <v>#VALUE!</v>
+      <c r="A293" t="str" cm="1">
+        <f t="array" ref="A293">_xlfn.TEXTJOIN(", ",TRUE,"a","",D!B1:B2)</f>
+        <v>a, 4, 8</v>
       </c>
       <c r="B293">
-        <f t="shared" ca="1" si="12"/>
-        <v>9</v>
+        <f t="shared" si="12"/>
+        <v>-3</v>
       </c>
       <c r="C293">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D293" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
+        <f t="shared" si="14"/>
+        <v>a, 4, 8</v>
       </c>
       <c r="E293" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A294" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A294" ca="1">TIME(12,{1;2},0)</f>
-        <v>#VALUE!</v>
+      <c r="A294" t="str" cm="1">
+        <f t="array" ref="A294">_xlfn.TEXTJOIN(", ",TRUE,"a","",{1;2})</f>
+        <v>a, 1, 2</v>
       </c>
       <c r="B294">
-        <f t="shared" ca="1" si="12"/>
-        <v>9</v>
+        <f t="shared" si="12"/>
+        <v>-3</v>
       </c>
       <c r="C294">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D294" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
+        <f t="shared" si="14"/>
+        <v>a, 1, 2</v>
       </c>
       <c r="E294" t="s">
         <v>342</v>
@@ -9221,7 +9221,7 @@
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A295" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A295" ca="1">TIME(12,0,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A295" ca="1">TIME(D!B1:B2,0,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B295">
@@ -9242,7 +9242,7 @@
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A296" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A296" ca="1">TIME(12,0,{1;2})</f>
+        <f t="array" aca="1" ref="A296" ca="1">TIME({1;2},0,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B296">
@@ -9263,7 +9263,7 @@
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A297" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A297" ca="1">TIMEVALUE(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A297" ca="1">TIME(12,D!B1:B2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B297">
@@ -9284,7 +9284,7 @@
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A298" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A298" ca="1">TIMEVALUE({1;2})</f>
+        <f t="array" aca="1" ref="A298" ca="1">TIME(12,{1;2},0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B298">
@@ -9305,7 +9305,7 @@
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A299" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A299" ca="1">TINV(D!B1:B2,60)</f>
+        <f t="array" aca="1" ref="A299" ca="1">TIME(12,0,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B299">
@@ -9326,7 +9326,7 @@
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A300" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A300" ca="1">TINV({1;2},60)</f>
+        <f t="array" aca="1" ref="A300" ca="1">TIME(12,0,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B300">
@@ -9347,7 +9347,7 @@
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A301" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A301" ca="1">TINV(0.05464493,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A301" ca="1">TIMEVALUE(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B301">
@@ -9368,7 +9368,7 @@
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A302" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A302" ca="1">TINV(0.05464493,{1;2})</f>
+        <f t="array" aca="1" ref="A302" ca="1">TIMEVALUE({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B302">
@@ -9389,7 +9389,7 @@
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A303" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A303" ca="1">TRIM(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A303" ca="1">TINV(D!B1:B2,60)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B303">
@@ -9410,7 +9410,7 @@
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A304" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A304" ca="1">TRIM({1;2})</f>
+        <f t="array" aca="1" ref="A304" ca="1">TINV({1;2},60)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B304">
@@ -9431,7 +9431,7 @@
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A305" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A305" ca="1">TRIMMEAN(D!B1:B8,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A305" ca="1">TINV(0.05464493,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B305">
@@ -9452,7 +9452,7 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A306" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A306" ca="1">TRIMMEAN(D!B1:B8,{1;2})</f>
+        <f t="array" aca="1" ref="A306" ca="1">TINV(0.05464493,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B306">
@@ -9473,7 +9473,7 @@
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A307" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A307" ca="1">TRUNC(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A307" ca="1">TRIM(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B307">
@@ -9494,7 +9494,7 @@
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A308" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A308" ca="1">TRUNC({1;2})</f>
+        <f t="array" aca="1" ref="A308" ca="1">TRIM({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B308">
@@ -9515,7 +9515,7 @@
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A309" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A309" ca="1">TTEST(D!B1:B8,D!C1:C8,D!B1:B2,1)</f>
+        <f t="array" aca="1" ref="A309" ca="1">TRIMMEAN(D!B1:B8,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B309">
@@ -9536,7 +9536,7 @@
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A310" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A310" ca="1">TTEST(D!B1:B8,D!C1:C8,{1;2},1)</f>
+        <f t="array" aca="1" ref="A310" ca="1">TRIMMEAN(D!B1:B8,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B310">
@@ -9557,7 +9557,7 @@
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A311" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A311" ca="1">TTEST(D!B1:B8,D!C1:C8,2,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A311" ca="1">TRUNC(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B311">
@@ -9578,7 +9578,7 @@
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A312" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A312" ca="1">TTEST(D!B1:B8,D!C1:C8,2,{1;2})</f>
+        <f t="array" aca="1" ref="A312" ca="1">TRUNC({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B312">
@@ -9598,125 +9598,125 @@
       </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A313" cm="1">
-        <f t="array" ref="A313">TYPE(D!B1:B2)</f>
+      <c r="A313" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A313" ca="1">TTEST(D!B1:B8,D!C1:C8,D!B1:B2,1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B313">
+        <f t="shared" ca="1" si="12"/>
+        <v>9</v>
+      </c>
+      <c r="C313">
+        <f t="shared" ca="1" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="D313" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="E313" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A314" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A314" ca="1">TTEST(D!B1:B8,D!C1:C8,{1;2},1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B314">
+        <f t="shared" ca="1" si="12"/>
+        <v>9</v>
+      </c>
+      <c r="C314">
+        <f t="shared" ca="1" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="D314" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="E314" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A315" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A315" ca="1">TTEST(D!B1:B8,D!C1:C8,2,D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B315">
+        <f t="shared" ca="1" si="12"/>
+        <v>9</v>
+      </c>
+      <c r="C315">
+        <f t="shared" ca="1" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="D315" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="E315" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A316" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A316" ca="1">TTEST(D!B1:B8,D!C1:C8,2,{1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B316">
+        <f t="shared" ca="1" si="12"/>
+        <v>9</v>
+      </c>
+      <c r="C316">
+        <f t="shared" ca="1" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="D316" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="E316" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A317" cm="1">
+        <f t="array" ref="A317">TYPE(D!B1:B2)</f>
         <v>64</v>
       </c>
-      <c r="B313">
+      <c r="B317">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="C313">
+      <c r="C317">
         <f t="shared" si="13"/>
         <v>64</v>
       </c>
-      <c r="D313" t="str">
+      <c r="D317" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="E313" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A314" cm="1">
-        <f t="array" ref="A314">TYPE({1;2})</f>
+      <c r="E317" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A318" cm="1">
+        <f t="array" ref="A318">TYPE({1;2})</f>
         <v>64</v>
       </c>
-      <c r="B314">
+      <c r="B318">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="C314">
+      <c r="C318">
         <f t="shared" si="13"/>
         <v>64</v>
       </c>
-      <c r="D314" t="str">
+      <c r="D318" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="E314" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A315" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A315" ca="1">_xlfn.UNICHAR(D!B1:B2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B315">
-        <f t="shared" ca="1" si="12"/>
-        <v>9</v>
-      </c>
-      <c r="C315">
-        <f t="shared" ca="1" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="D315" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-      <c r="E315" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A316" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A316" ca="1">_xlfn.UNICHAR({1;2})</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B316">
-        <f t="shared" ca="1" si="12"/>
-        <v>9</v>
-      </c>
-      <c r="C316">
-        <f t="shared" ca="1" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="D316" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-      <c r="E316" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A317" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A317" ca="1">_xlfn.UNICODE(D!B1:B2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B317">
-        <f t="shared" ca="1" si="12"/>
-        <v>9</v>
-      </c>
-      <c r="C317">
-        <f t="shared" ca="1" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="D317" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-      <c r="E317" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A318" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A318" ca="1">_xlfn.UNICODE({1;2})</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B318">
-        <f t="shared" ca="1" si="12"/>
-        <v>9</v>
-      </c>
-      <c r="C318">
-        <f t="shared" ca="1" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="D318" t="str">
-        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="E318" t="s">
@@ -9725,7 +9725,7 @@
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A319" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A319" ca="1">UPPER(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A319" ca="1">_xlfn.UNICHAR(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B319">
@@ -9746,7 +9746,7 @@
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A320" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A320" ca="1">UPPER({1;2})</f>
+        <f t="array" aca="1" ref="A320" ca="1">_xlfn.UNICHAR({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B320">
@@ -9767,7 +9767,7 @@
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A321" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A321" ca="1">VALUE(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A321" ca="1">_xlfn.UNICODE(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B321">
@@ -9788,7 +9788,7 @@
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A322" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A322" ca="1">VALUE({1;2})</f>
+        <f t="array" aca="1" ref="A322" ca="1">_xlfn.UNICODE({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B322">
@@ -9809,7 +9809,7 @@
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A323" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A323" ca="1">_xlfn.VALUETOTEXT(D!B1:B2,0)</f>
+        <f t="array" aca="1" ref="A323" ca="1">UPPER(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B323">
@@ -9830,7 +9830,7 @@
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A324" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A324" ca="1">_xlfn.VALUETOTEXT({1;2},0)</f>
+        <f t="array" aca="1" ref="A324" ca="1">UPPER({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B324">
@@ -9851,7 +9851,7 @@
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A325" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A325" ca="1">_xlfn.VALUETOTEXT(1.5,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A325" ca="1">VALUE(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B325">
@@ -9872,7 +9872,7 @@
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A326" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A326" ca="1">_xlfn.VALUETOTEXT(1.5,{1;2})</f>
+        <f t="array" aca="1" ref="A326" ca="1">VALUE({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B326">
@@ -9892,272 +9892,272 @@
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A327" cm="1">
-        <f t="array" ref="A327">VAR(D!B1:B2,2,4)</f>
+      <c r="A327" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A327" ca="1">_xlfn.VALUETOTEXT(D!B1:B2,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B327">
+        <f t="shared" ca="1" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="C327">
+        <f t="shared" ca="1" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="D327" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="E327" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A328" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A328" ca="1">_xlfn.VALUETOTEXT({1;2},0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B328">
+        <f t="shared" ca="1" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="C328">
+        <f t="shared" ca="1" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="D328" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="E328" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A329" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A329" ca="1">_xlfn.VALUETOTEXT(1.5,D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B329">
+        <f t="shared" ca="1" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="C329">
+        <f t="shared" ca="1" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="D329" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="E329" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A330" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A330" ca="1">_xlfn.VALUETOTEXT(1.5,{1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B330">
+        <f t="shared" ca="1" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="C330">
+        <f t="shared" ca="1" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="D330" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="E330" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A331" cm="1">
+        <f t="array" ref="A331">VAR(D!B1:B2,2,4)</f>
         <v>6.333333333333333</v>
       </c>
-      <c r="B327">
+      <c r="B331">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="C327">
+      <c r="C331">
         <f t="shared" si="16"/>
         <v>6.333333333333333</v>
       </c>
-      <c r="D327" t="str">
+      <c r="D331" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="E327" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A328" cm="1">
-        <f t="array" ref="A328">VAR({1;2},2,4)</f>
+      <c r="E331" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A332" cm="1">
+        <f t="array" ref="A332">VAR({1;2},2,4)</f>
         <v>1.5833333333333333</v>
       </c>
-      <c r="B328">
+      <c r="B332">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="C328">
+      <c r="C332">
         <f t="shared" si="16"/>
         <v>1.5833333333333333</v>
       </c>
-      <c r="D328" t="str">
+      <c r="D332" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="E328" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A329" cm="1">
-        <f t="array" ref="A329">VAR(1,D!B1:B2,4)</f>
+      <c r="E332" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A333" cm="1">
+        <f t="array" ref="A333">VAR(1,D!B1:B2,4)</f>
         <v>8.25</v>
       </c>
-      <c r="B329">
+      <c r="B333">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="C329">
+      <c r="C333">
         <f t="shared" si="16"/>
         <v>8.25</v>
       </c>
-      <c r="D329" t="str">
+      <c r="D333" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="E329" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A330" cm="1">
-        <f t="array" ref="A330">VAR(1,{1;2},4)</f>
+      <c r="E333" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A334" cm="1">
+        <f t="array" ref="A334">VAR(1,{1;2},4)</f>
         <v>2</v>
       </c>
-      <c r="B330">
+      <c r="B334">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="C330">
+      <c r="C334">
         <f t="shared" si="16"/>
         <v>2</v>
       </c>
-      <c r="D330" t="str">
+      <c r="D334" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="E330" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A331" cm="1">
-        <f t="array" ref="A331">VAR(1,2,D!B1:B2)</f>
+      <c r="E334" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A335" cm="1">
+        <f t="array" ref="A335">VAR(1,2,D!B1:B2)</f>
         <v>9.5833333333333339</v>
       </c>
-      <c r="B331">
+      <c r="B335">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="C331">
+      <c r="C335">
         <f t="shared" si="16"/>
         <v>9.5833333333333339</v>
       </c>
-      <c r="D331" t="str">
+      <c r="D335" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="E331" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A332" cm="1">
-        <f t="array" ref="A332">VAR(1,2,{1;2})</f>
+      <c r="E335" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A336" cm="1">
+        <f t="array" ref="A336">VAR(1,2,{1;2})</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="B332">
+      <c r="B336">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="C332">
+      <c r="C336">
         <f t="shared" si="16"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="D332" t="str">
+      <c r="D336" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="E332" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A333" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A333" ca="1">VLOOKUP(D!B1:B2,D!L1:N6,2,FALSE)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B333">
+      <c r="E336" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A337" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A337" ca="1">VLOOKUP(D!B1:B2,D!L1:N6,2,FALSE)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B337">
         <f t="shared" ca="1" si="15"/>
         <v>9</v>
       </c>
-      <c r="C333">
+      <c r="C337">
         <f t="shared" ca="1" si="16"/>
         <v>0</v>
       </c>
-      <c r="D333" t="str">
+      <c r="D337" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="E333" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A334" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A334" ca="1">VLOOKUP({1;2},D!L1:N6,2,FALSE)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B334">
+      <c r="E337" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A338" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A338" ca="1">VLOOKUP({1;2},D!L1:N6,2,FALSE)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B338">
         <f t="shared" ca="1" si="15"/>
         <v>9</v>
       </c>
-      <c r="C334">
+      <c r="C338">
         <f t="shared" ca="1" si="16"/>
         <v>0</v>
       </c>
-      <c r="D334" t="str">
+      <c r="D338" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="E334" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A335" t="e" cm="1">
-        <f t="array" ref="A335">VLOOKUP(5,D!L1:N6,D!B1:B2,FALSE)</f>
+      <c r="E338" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A339" t="e" cm="1">
+        <f t="array" ref="A339">VLOOKUP(5,D!L1:N6,D!B1:B2,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="B335">
+      <c r="B339">
         <f t="shared" si="15"/>
         <v>4</v>
       </c>
-      <c r="C335">
+      <c r="C339">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="D335" t="str">
+      <c r="D339" t="str">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="E335" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A336" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A336" ca="1">VLOOKUP(5,D!L1:N6,{1;2},FALSE)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B336">
-        <f t="shared" ca="1" si="15"/>
-        <v>9</v>
-      </c>
-      <c r="C336">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="D336" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="E336" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A337" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A337" ca="1">VLOOKUP(5,D!L1:N6,2,D!B1:B2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B337">
-        <f t="shared" ca="1" si="15"/>
-        <v>9</v>
-      </c>
-      <c r="C337">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="D337" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="E337" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A338" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A338" ca="1">VLOOKUP(5,D!L1:N6,2,{1;2})</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B338">
-        <f t="shared" ca="1" si="15"/>
-        <v>9</v>
-      </c>
-      <c r="C338">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="D338" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="E338" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A339" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A339" ca="1">WEEKDAY(D!B1:B2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B339">
-        <f t="shared" ca="1" si="15"/>
-        <v>9</v>
-      </c>
-      <c r="C339">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="D339" t="str">
-        <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
       <c r="E339" t="s">
@@ -10166,7 +10166,7 @@
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A340" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A340" ca="1">WEEKDAY({1;2})</f>
+        <f t="array" aca="1" ref="A340" ca="1">VLOOKUP(5,D!L1:N6,{1;2},FALSE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B340">
@@ -10186,104 +10186,104 @@
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A341" t="e" cm="1">
-        <f t="array" ref="A341">WEEKNUM(D!B1:B2)</f>
+      <c r="A341" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A341" ca="1">VLOOKUP(5,D!L1:N6,2,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B341">
+        <f t="shared" ca="1" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="C341">
+        <f t="shared" ca="1" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="D341" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="E341" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A342" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A342" ca="1">VLOOKUP(5,D!L1:N6,2,{1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B342">
+        <f t="shared" ca="1" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="C342">
+        <f t="shared" ca="1" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="D342" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="E342" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A343" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A343" ca="1">WEEKDAY(D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B343">
+        <f t="shared" ca="1" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="C343">
+        <f t="shared" ca="1" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="D343" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="E343" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A344" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A344" ca="1">WEEKDAY({1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B344">
+        <f t="shared" ca="1" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="C344">
+        <f t="shared" ca="1" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="D344" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="E344" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A345" t="e" cm="1">
+        <f t="array" ref="A345">WEEKNUM(D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B345">
         <f t="shared" si="15"/>
         <v>3</v>
       </c>
-      <c r="C341">
+      <c r="C345">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="D341" t="str">
+      <c r="D345" t="str">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="E341" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A342" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A342" ca="1">WEEKNUM({1;2})</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B342">
-        <f t="shared" ca="1" si="15"/>
-        <v>9</v>
-      </c>
-      <c r="C342">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="D342" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="E342" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A343" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A343" ca="1">WEIBULL(D!B1:B2,20,100,TRUE)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B343">
-        <f t="shared" ca="1" si="15"/>
-        <v>9</v>
-      </c>
-      <c r="C343">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="D343" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="E343" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A344" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A344" ca="1">WEIBULL({1;2},20,100,TRUE)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B344">
-        <f t="shared" ca="1" si="15"/>
-        <v>9</v>
-      </c>
-      <c r="C344">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="D344" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="E344" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A345" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A345" ca="1">WEIBULL(105,D!B1:B2,100,TRUE)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B345">
-        <f t="shared" ca="1" si="15"/>
-        <v>9</v>
-      </c>
-      <c r="C345">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="D345" t="str">
-        <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
       <c r="E345" t="s">
@@ -10292,7 +10292,7 @@
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A346" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A346" ca="1">WEIBULL(105,{1;2},100,TRUE)</f>
+        <f t="array" aca="1" ref="A346" ca="1">WEEKNUM({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B346">
@@ -10313,7 +10313,7 @@
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A347" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A347" ca="1">WEIBULL(105,20,D!B1:B2,TRUE)</f>
+        <f t="array" aca="1" ref="A347" ca="1">WEIBULL(D!B1:B2,20,100,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B347">
@@ -10334,7 +10334,7 @@
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A348" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A348" ca="1">WEIBULL(105,20,{1;2},TRUE)</f>
+        <f t="array" aca="1" ref="A348" ca="1">WEIBULL({1;2},20,100,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B348">
@@ -10355,7 +10355,7 @@
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A349" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A349" ca="1">WEIBULL(105,20,100,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A349" ca="1">WEIBULL(105,D!B1:B2,100,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B349">
@@ -10376,7 +10376,7 @@
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A350" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A350" ca="1">WEIBULL(105,20,100,{1;2})</f>
+        <f t="array" aca="1" ref="A350" ca="1">WEIBULL(105,{1;2},100,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B350">
@@ -10397,7 +10397,7 @@
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A351" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A351" ca="1">_xlfn.WEIBULL.DIST(D!B1:B2,20,100,TRUE)</f>
+        <f t="array" aca="1" ref="A351" ca="1">WEIBULL(105,20,D!B1:B2,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B351">
@@ -10418,7 +10418,7 @@
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A352" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A352" ca="1">_xlfn.WEIBULL.DIST({1;2},20,100,TRUE)</f>
+        <f t="array" aca="1" ref="A352" ca="1">WEIBULL(105,20,{1;2},TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B352">
@@ -10439,7 +10439,7 @@
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A353" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A353" ca="1">_xlfn.WEIBULL.DIST(105,D!B1:B2,100,TRUE)</f>
+        <f t="array" aca="1" ref="A353" ca="1">WEIBULL(105,20,100,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B353">
@@ -10460,7 +10460,7 @@
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A354" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A354" ca="1">_xlfn.WEIBULL.DIST(105,{1;2},100,TRUE)</f>
+        <f t="array" aca="1" ref="A354" ca="1">WEIBULL(105,20,100,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B354">
@@ -10481,7 +10481,7 @@
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A355" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A355" ca="1">_xlfn.WEIBULL.DIST(105,20,D!B1:B2,TRUE)</f>
+        <f t="array" aca="1" ref="A355" ca="1">_xlfn.WEIBULL.DIST(D!B1:B2,20,100,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B355">
@@ -10502,7 +10502,7 @@
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A356" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A356" ca="1">_xlfn.WEIBULL.DIST(105,20,{1;2},TRUE)</f>
+        <f t="array" aca="1" ref="A356" ca="1">_xlfn.WEIBULL.DIST({1;2},20,100,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B356">
@@ -10523,7 +10523,7 @@
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A357" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A357" ca="1">_xlfn.WEIBULL.DIST(105,20,100,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A357" ca="1">_xlfn.WEIBULL.DIST(105,D!B1:B2,100,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B357">
@@ -10544,7 +10544,7 @@
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A358" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A358" ca="1">_xlfn.WEIBULL.DIST(105,20,100,{1;2})</f>
+        <f t="array" aca="1" ref="A358" ca="1">_xlfn.WEIBULL.DIST(105,{1;2},100,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B358">
@@ -10564,20 +10564,20 @@
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A359" t="e" cm="1">
-        <f t="array" ref="A359">WORKDAY(D!B1:B2,151)</f>
+      <c r="A359" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A359" ca="1">_xlfn.WEIBULL.DIST(105,20,D!B1:B2,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B359">
-        <f t="shared" si="15"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>9</v>
       </c>
       <c r="C359">
-        <f t="shared" si="16"/>
+        <f t="shared" ca="1" si="16"/>
         <v>0</v>
       </c>
       <c r="D359" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
       <c r="E359" t="s">
@@ -10586,7 +10586,7 @@
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A360" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A360" ca="1">WORKDAY({1;2},151)</f>
+        <f t="array" aca="1" ref="A360" ca="1">_xlfn.WEIBULL.DIST(105,20,{1;2},TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B360">
@@ -10606,20 +10606,20 @@
       </c>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A361" t="e" cm="1">
-        <f t="array" ref="A361">WORKDAY(39722,D!B1:B2)</f>
+      <c r="A361" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A361" ca="1">_xlfn.WEIBULL.DIST(105,20,100,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B361">
-        <f t="shared" si="15"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>9</v>
       </c>
       <c r="C361">
-        <f t="shared" si="16"/>
+        <f t="shared" ca="1" si="16"/>
         <v>0</v>
       </c>
       <c r="D361" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
       <c r="E361" t="s">
@@ -10628,7 +10628,7 @@
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A362" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A362" ca="1">WORKDAY(39722,{1;2})</f>
+        <f t="array" aca="1" ref="A362" ca="1">_xlfn.WEIBULL.DIST(105,20,100,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B362">
@@ -10649,7 +10649,7 @@
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A363" t="e" cm="1">
-        <f t="array" ref="A363">WORKDAY.INTL(D!B1:B2,90,11)</f>
+        <f t="array" ref="A363">WORKDAY(D!B1:B2,151)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B363">
@@ -10670,7 +10670,7 @@
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A364" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A364" ca="1">WORKDAY.INTL({1;2},90,11)</f>
+        <f t="array" aca="1" ref="A364" ca="1">WORKDAY({1;2},151)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B364">
@@ -10691,7 +10691,7 @@
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A365" t="e" cm="1">
-        <f t="array" ref="A365">WORKDAY.INTL(40909,D!B1:B2,11)</f>
+        <f t="array" ref="A365">WORKDAY(39722,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B365">
@@ -10712,7 +10712,7 @@
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A366" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A366" ca="1">WORKDAY.INTL(40909,{1;2},11)</f>
+        <f t="array" aca="1" ref="A366" ca="1">WORKDAY(39722,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B366">
@@ -10732,20 +10732,20 @@
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A367" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A367" ca="1">WORKDAY.INTL(40909,90,D!B1:B2)</f>
+      <c r="A367" t="e" cm="1">
+        <f t="array" ref="A367">WORKDAY.INTL(D!B1:B2,90,11)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B367">
-        <f t="shared" ca="1" si="15"/>
-        <v>9</v>
+        <f t="shared" si="15"/>
+        <v>3</v>
       </c>
       <c r="C367">
-        <f t="shared" ca="1" si="16"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="D367" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="E367" t="s">
@@ -10754,7 +10754,7 @@
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A368" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A368" ca="1">WORKDAY.INTL(40909,90,{1;2})</f>
+        <f t="array" aca="1" ref="A368" ca="1">WORKDAY.INTL({1;2},90,11)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B368">
@@ -10774,20 +10774,20 @@
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A369" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A369" ca="1">_xlfn.XLOOKUP(D!B1:B2,D!L1:L6,D!M1:M6)</f>
+      <c r="A369" t="e" cm="1">
+        <f t="array" ref="A369">WORKDAY.INTL(40909,D!B1:B2,11)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B369">
-        <f t="shared" ca="1" si="15"/>
-        <v>9</v>
+        <f t="shared" si="15"/>
+        <v>3</v>
       </c>
       <c r="C369">
-        <f t="shared" ca="1" si="16"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="D369" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="E369" t="s">
@@ -10796,7 +10796,7 @@
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A370" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A370" ca="1">_xlfn.XLOOKUP({1;2},D!L1:L6,D!M1:M6)</f>
+        <f t="array" aca="1" ref="A370" ca="1">WORKDAY.INTL(40909,{1;2},11)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B370">
@@ -10817,7 +10817,7 @@
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A371" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A371" ca="1">_xlfn.XMATCH(D!B1:B2,D!L1:L6)</f>
+        <f t="array" aca="1" ref="A371" ca="1">WORKDAY.INTL(40909,90,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B371">
@@ -10838,7 +10838,7 @@
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A372" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A372" ca="1">_xlfn.XMATCH({1;2},D!L1:L6)</f>
+        <f t="array" aca="1" ref="A372" ca="1">WORKDAY.INTL(40909,90,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B372">
@@ -10858,209 +10858,209 @@
       </c>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A373" t="e" cm="1">
-        <f t="array" ref="A373">XNPV(D!B1:B2,D!J1:J5,D!AU1:AU5)</f>
+      <c r="A373" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A373" ca="1">_xlfn.XLOOKUP(D!B1:B2,D!L1:L6,D!M1:M6)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B373">
+        <f t="shared" ca="1" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="C373">
+        <f t="shared" ca="1" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="D373" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="E373" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A374" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A374" ca="1">_xlfn.XLOOKUP({1;2},D!L1:L6,D!M1:M6)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B374">
+        <f t="shared" ca="1" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="C374">
+        <f t="shared" ca="1" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="D374" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="E374" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A375" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A375" ca="1">_xlfn.XMATCH(D!B1:B2,D!L1:L6)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B375">
+        <f t="shared" ca="1" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="C375">
+        <f t="shared" ca="1" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="D375" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="E375" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A376" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A376" ca="1">_xlfn.XMATCH({1;2},D!L1:L6)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B376">
+        <f t="shared" ca="1" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="C376">
+        <f t="shared" ca="1" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="D376" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="E376" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A377" t="e" cm="1">
+        <f t="array" ref="A377">XNPV(D!B1:B2,D!J1:J5,D!AU1:AU5)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B377">
         <f t="shared" si="15"/>
         <v>3</v>
       </c>
-      <c r="C373">
+      <c r="C377">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="D373" t="str">
+      <c r="D377" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="E373" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A374" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A374" ca="1">XNPV({1;2},D!J1:J5,D!AU1:AU5)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B374">
+      <c r="E377" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A378" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A378" ca="1">XNPV({1;2},D!J1:J5,D!AU1:AU5)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B378">
         <f t="shared" ca="1" si="15"/>
         <v>9</v>
       </c>
-      <c r="C374">
+      <c r="C378">
         <f t="shared" ca="1" si="16"/>
         <v>0</v>
       </c>
-      <c r="D374" t="str">
+      <c r="D378" t="str">
         <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
-      <c r="E374" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A375" t="b" cm="1">
-        <f t="array" ref="A375">_xlfn.XOR(D!B1:B2,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="B375">
+      <c r="E378" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A379" t="b" cm="1">
+        <f t="array" ref="A379">_xlfn.XOR(D!B1:B2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="B379">
         <f t="shared" si="15"/>
         <v>-2</v>
       </c>
-      <c r="C375">
+      <c r="C379">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="D375" t="str">
+      <c r="D379" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="E375" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A376" t="b" cm="1">
-        <f t="array" ref="A376">_xlfn.XOR({1;2},FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="B376">
+      <c r="E379" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A380" t="b" cm="1">
+        <f t="array" ref="A380">_xlfn.XOR({1;2},FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="B380">
         <f t="shared" si="15"/>
         <v>-2</v>
       </c>
-      <c r="C376">
+      <c r="C380">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="D376" t="str">
+      <c r="D380" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="E376" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A377" t="b" cm="1">
-        <f t="array" ref="A377">_xlfn.XOR(TRUE,D!B1:B2)</f>
+      <c r="E380" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A381" t="b" cm="1">
+        <f t="array" ref="A381">_xlfn.XOR(TRUE,D!B1:B2)</f>
         <v>1</v>
       </c>
-      <c r="B377">
+      <c r="B381">
         <f t="shared" si="15"/>
         <v>-1</v>
       </c>
-      <c r="C377">
+      <c r="C381">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="D377" t="str">
+      <c r="D381" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="E377" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A378" t="b" cm="1">
-        <f t="array" ref="A378">_xlfn.XOR(TRUE,{1;2})</f>
+      <c r="E381" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A382" t="b" cm="1">
+        <f t="array" ref="A382">_xlfn.XOR(TRUE,{1;2})</f>
         <v>1</v>
       </c>
-      <c r="B378">
+      <c r="B382">
         <f t="shared" si="15"/>
         <v>-1</v>
       </c>
-      <c r="C378">
+      <c r="C382">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="D378" t="str">
+      <c r="D382" t="str">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="E378" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A379" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A379" ca="1">YEAR(D!B1:B2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B379">
-        <f t="shared" ca="1" si="15"/>
-        <v>9</v>
-      </c>
-      <c r="C379">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="D379" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="E379" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A380" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A380" ca="1">YEAR({1;2})</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B380">
-        <f t="shared" ca="1" si="15"/>
-        <v>9</v>
-      </c>
-      <c r="C380">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="D380" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="E380" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A381" t="e" cm="1">
-        <f t="array" ref="A381">YEARFRAC(D!B1:B2,41120)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B381">
-        <f t="shared" si="15"/>
-        <v>3</v>
-      </c>
-      <c r="C381">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="D381" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="E381" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A382" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A382" ca="1">YEARFRAC({1;2},41120)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B382">
-        <f t="shared" ca="1" si="15"/>
-        <v>9</v>
-      </c>
-      <c r="C382">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="D382" t="str">
-        <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
       <c r="E382" t="s">
@@ -11068,20 +11068,20 @@
       </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A383" t="e" cm="1">
-        <f t="array" ref="A383">YEARFRAC(40909,D!B1:B2)</f>
+      <c r="A383" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A383" ca="1">YEAR(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B383">
-        <f t="shared" si="15"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>9</v>
       </c>
       <c r="C383">
-        <f t="shared" si="16"/>
+        <f t="shared" ca="1" si="16"/>
         <v>0</v>
       </c>
       <c r="D383" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
       <c r="E383" t="s">
@@ -11090,7 +11090,7 @@
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A384" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A384" ca="1">YEARFRAC(40909,{1;2})</f>
+        <f t="array" aca="1" ref="A384" ca="1">YEAR({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B384">
@@ -11111,7 +11111,7 @@
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A385" t="e" cm="1">
-        <f t="array" ref="A385">YIELD(D!B1:B2,DATE(2016,11,15),0.0575,95.04287,100,2,0)</f>
+        <f t="array" ref="A385">YEARFRAC(D!B1:B2,41120)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B385">
@@ -11132,7 +11132,7 @@
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A386" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A386" ca="1">YIELD({1;2},DATE(2016,11,15),0.0575,95.04287,100,2,0)</f>
+        <f t="array" aca="1" ref="A386" ca="1">YEARFRAC({1;2},41120)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B386">
@@ -11153,7 +11153,7 @@
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A387" t="e" cm="1">
-        <f t="array" ref="A387">YIELD(DATE(2008,2,15),D!B1:B2,0.0575,95.04287,100,2,0)</f>
+        <f t="array" ref="A387">YEARFRAC(40909,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B387">
@@ -11174,7 +11174,7 @@
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A388" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A388" ca="1">YIELD(DATE(2008,2,15),{1;2},0.0575,95.04287,100,2,0)</f>
+        <f t="array" aca="1" ref="A388" ca="1">YEARFRAC(40909,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B388">
@@ -11195,7 +11195,7 @@
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A389" t="e" cm="1">
-        <f t="array" ref="A389">YIELD(DATE(2008,2,15),DATE(2016,11,15),D!B1:B2,95.04287,100,2,0)</f>
+        <f t="array" ref="A389">YIELD(D!B1:B2,DATE(2016,11,15),0.0575,95.04287,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B389">
@@ -11216,7 +11216,7 @@
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A390" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A390" ca="1">YIELD(DATE(2008,2,15),DATE(2016,11,15),{1;2},95.04287,100,2,0)</f>
+        <f t="array" aca="1" ref="A390" ca="1">YIELD({1;2},DATE(2016,11,15),0.0575,95.04287,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B390">
@@ -11237,7 +11237,7 @@
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A391" t="e" cm="1">
-        <f t="array" ref="A391">YIELD(DATE(2008,2,15),DATE(2016,11,15),0.0575,D!B1:B2,100,2,0)</f>
+        <f t="array" ref="A391">YIELD(DATE(2008,2,15),D!B1:B2,0.0575,95.04287,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B391">
@@ -11258,7 +11258,7 @@
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A392" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A392" ca="1">YIELD(DATE(2008,2,15),DATE(2016,11,15),0.0575,{1;2},100,2,0)</f>
+        <f t="array" aca="1" ref="A392" ca="1">YIELD(DATE(2008,2,15),{1;2},0.0575,95.04287,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B392">
@@ -11279,7 +11279,7 @@
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A393" t="e" cm="1">
-        <f t="array" ref="A393">YIELD(DATE(2008,2,15),DATE(2016,11,15),0.0575,95.04287,D!B1:B2,2,0)</f>
+        <f t="array" ref="A393">YIELD(DATE(2008,2,15),DATE(2016,11,15),D!B1:B2,95.04287,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B393">
@@ -11300,7 +11300,7 @@
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A394" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A394" ca="1">YIELD(DATE(2008,2,15),DATE(2016,11,15),0.0575,95.04287,{1;2},2,0)</f>
+        <f t="array" aca="1" ref="A394" ca="1">YIELD(DATE(2008,2,15),DATE(2016,11,15),{1;2},95.04287,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B394">
@@ -11321,7 +11321,7 @@
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A395" t="e" cm="1">
-        <f t="array" ref="A395">YIELD(DATE(2008,2,15),DATE(2016,11,15),0.0575,95.04287,100,D!B1:B2,0)</f>
+        <f t="array" ref="A395">YIELD(DATE(2008,2,15),DATE(2016,11,15),0.0575,D!B1:B2,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B395">
@@ -11342,7 +11342,7 @@
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A396" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A396" ca="1">YIELD(DATE(2008,2,15),DATE(2016,11,15),0.0575,95.04287,100,{1;2},0)</f>
+        <f t="array" aca="1" ref="A396" ca="1">YIELD(DATE(2008,2,15),DATE(2016,11,15),0.0575,{1;2},100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B396">
@@ -11363,7 +11363,7 @@
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A397" t="e" cm="1">
-        <f t="array" ref="A397">YIELD(DATE(2008,2,15),DATE(2016,11,15),0.0575,95.04287,100,2,D!B1:B2)</f>
+        <f t="array" ref="A397">YIELD(DATE(2008,2,15),DATE(2016,11,15),0.0575,95.04287,D!B1:B2,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B397">
@@ -11384,7 +11384,7 @@
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A398" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A398" ca="1">YIELD(DATE(2008,2,15),DATE(2016,11,15),0.0575,95.04287,100,2,{1;2})</f>
+        <f t="array" aca="1" ref="A398" ca="1">YIELD(DATE(2008,2,15),DATE(2016,11,15),0.0575,95.04287,{1;2},2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B398">
@@ -11405,7 +11405,7 @@
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A399" t="e" cm="1">
-        <f t="array" ref="A399">YIELDDISC(D!B1:B2,DATE(2008,3,1),99.795,100,2)</f>
+        <f t="array" ref="A399">YIELD(DATE(2008,2,15),DATE(2016,11,15),0.0575,95.04287,100,D!B1:B2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B399">
@@ -11426,7 +11426,7 @@
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A400" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A400" ca="1">YIELDDISC({1;2},DATE(2008,3,1),99.795,100,2)</f>
+        <f t="array" aca="1" ref="A400" ca="1">YIELD(DATE(2008,2,15),DATE(2016,11,15),0.0575,95.04287,100,{1;2},0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B400">
